--- a/normalized_outputs/normalized_vacancy_rate_by_tract_deltas.xlsx
+++ b/normalized_outputs/normalized_vacancy_rate_by_tract_deltas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F963"/>
+  <dimension ref="A1:G963"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -382,6 +382,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>vacancy_delta_zscore_raw</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>vacancy_delta_zscore</t>
         </is>
       </c>
@@ -402,6 +407,9 @@
       <c r="F2">
         <v>-0.01792803205554807</v>
       </c>
+      <c r="G2">
+        <v>-0.01792803205554807</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -419,6 +427,9 @@
       <c r="F3">
         <v>-0.8170596108324928</v>
       </c>
+      <c r="G3">
+        <v>-0.8170596108324928</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -436,6 +447,9 @@
       <c r="F4">
         <v>-0.6832841221073508</v>
       </c>
+      <c r="G4">
+        <v>-0.6832841221073508</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -453,6 +467,9 @@
       <c r="F5">
         <v>-0.7267070593316716</v>
       </c>
+      <c r="G5">
+        <v>-0.7267070593316716</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -470,6 +487,9 @@
       <c r="F6">
         <v>-0.6311632977588902</v>
       </c>
+      <c r="G6">
+        <v>-0.6311632977588902</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -487,6 +507,9 @@
       <c r="F7">
         <v>1.138248391169008</v>
       </c>
+      <c r="G7">
+        <v>1.138248391169008</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -504,6 +527,9 @@
       <c r="F8">
         <v>0.3667493528894131</v>
       </c>
+      <c r="G8">
+        <v>0.3667493528894131</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -521,6 +547,9 @@
       <c r="F9">
         <v>0.4094839775858813</v>
       </c>
+      <c r="G9">
+        <v>0.4094839775858813</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -538,6 +567,9 @@
       <c r="F10">
         <v>0.2501136292190203</v>
       </c>
+      <c r="G10">
+        <v>0.2501136292190203</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -555,6 +587,9 @@
       <c r="F11">
         <v>0.1141958916254291</v>
       </c>
+      <c r="G11">
+        <v>0.1141958916254291</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -572,6 +607,9 @@
       <c r="F12">
         <v>-0.3071172681250067</v>
       </c>
+      <c r="G12">
+        <v>-0.3071172681250067</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -589,6 +627,9 @@
       <c r="F13">
         <v>1.7419011151292</v>
       </c>
+      <c r="G13">
+        <v>1.7419011151292</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -606,6 +647,9 @@
       <c r="F14">
         <v>2.232423930122133</v>
       </c>
+      <c r="G14">
+        <v>2.232423930122133</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -623,6 +667,9 @@
       <c r="F15">
         <v>3.169795675599501</v>
       </c>
+      <c r="G15">
+        <v>3.169795675599501</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -640,6 +687,9 @@
       <c r="F16">
         <v>3.092988736506623</v>
       </c>
+      <c r="G16">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -657,6 +707,9 @@
       <c r="F17">
         <v>0.1051286489659462</v>
       </c>
+      <c r="G17">
+        <v>0.1051286489659462</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -674,6 +727,9 @@
       <c r="F18">
         <v>0.3945739472504945</v>
       </c>
+      <c r="G18">
+        <v>0.3945739472504945</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -691,6 +747,9 @@
       <c r="F19">
         <v>0.383088151925419</v>
       </c>
+      <c r="G19">
+        <v>0.383088151925419</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -708,6 +767,9 @@
       <c r="F20">
         <v>0.229016112155031</v>
       </c>
+      <c r="G20">
+        <v>0.229016112155031</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -725,6 +787,9 @@
       <c r="F21">
         <v>0.09393574145064831</v>
       </c>
+      <c r="G21">
+        <v>0.09393574145064831</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -742,6 +807,9 @@
       <c r="F22">
         <v>0.04432886309672798</v>
       </c>
+      <c r="G22">
+        <v>0.04432886309672798</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -759,6 +827,9 @@
       <c r="F23">
         <v>-0.2619952069027374</v>
       </c>
+      <c r="G23">
+        <v>-0.2619952069027374</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -776,6 +847,9 @@
       <c r="F24">
         <v>-0.1739076770086797</v>
       </c>
+      <c r="G24">
+        <v>-0.1739076770086797</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -793,6 +867,9 @@
       <c r="F25">
         <v>-0.306544805311287</v>
       </c>
+      <c r="G25">
+        <v>-0.306544805311287</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -810,6 +887,9 @@
       <c r="F26">
         <v>-0.3448794003516336</v>
       </c>
+      <c r="G26">
+        <v>-0.3448794003516336</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -827,6 +907,9 @@
       <c r="F27">
         <v>0.4252503135851525</v>
       </c>
+      <c r="G27">
+        <v>0.4252503135851525</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -844,6 +927,9 @@
       <c r="F28">
         <v>1.391719849904501</v>
       </c>
+      <c r="G28">
+        <v>1.391719849904501</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -861,6 +947,9 @@
       <c r="F29">
         <v>1.125029716809459</v>
       </c>
+      <c r="G29">
+        <v>1.125029716809459</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -878,6 +967,9 @@
       <c r="F30">
         <v>0.7304578818773309</v>
       </c>
+      <c r="G30">
+        <v>0.7304578818773309</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -895,6 +987,9 @@
       <c r="F31">
         <v>0.3831366134834674</v>
       </c>
+      <c r="G31">
+        <v>0.3831366134834674</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -912,6 +1007,9 @@
       <c r="F32">
         <v>0.005741784711025746</v>
       </c>
+      <c r="G32">
+        <v>0.005741784711025746</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -929,6 +1027,9 @@
       <c r="F33">
         <v>-0.6274286414165339</v>
       </c>
+      <c r="G33">
+        <v>-0.6274286414165339</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -946,6 +1047,9 @@
       <c r="F34">
         <v>-0.5208837220254158</v>
       </c>
+      <c r="G34">
+        <v>-0.5208837220254158</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -963,6 +1067,9 @@
       <c r="F35">
         <v>-0.6011410123429041</v>
       </c>
+      <c r="G35">
+        <v>-0.6011410123429041</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -980,6 +1087,9 @@
       <c r="F36">
         <v>-0.5507280957450509</v>
       </c>
+      <c r="G36">
+        <v>-0.5507280957450509</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -997,6 +1107,9 @@
       <c r="F37">
         <v>-0.367749330897875</v>
       </c>
+      <c r="G37">
+        <v>-0.367749330897875</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1014,6 +1127,9 @@
       <c r="F38">
         <v>-0.0518606751669374</v>
       </c>
+      <c r="G38">
+        <v>-0.0518606751669374</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1031,6 +1147,9 @@
       <c r="F39">
         <v>-1.016623460452568</v>
       </c>
+      <c r="G39">
+        <v>-1.016623460452568</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1048,6 +1167,9 @@
       <c r="F40">
         <v>-0.5071871531462413</v>
       </c>
+      <c r="G40">
+        <v>-0.5071871531462413</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1065,6 +1187,9 @@
       <c r="F41">
         <v>-0.6687147656989795</v>
       </c>
+      <c r="G41">
+        <v>-0.6687147656989795</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1082,6 +1207,9 @@
       <c r="F42">
         <v>0.2693091259508394</v>
       </c>
+      <c r="G42">
+        <v>0.2693091259508394</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1099,6 +1227,9 @@
       <c r="F43">
         <v>0.68974841711396</v>
       </c>
+      <c r="G43">
+        <v>0.68974841711396</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1116,6 +1247,9 @@
       <c r="F44">
         <v>0.6779281337277545</v>
       </c>
+      <c r="G44">
+        <v>0.6779281337277545</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1133,6 +1267,9 @@
       <c r="F45">
         <v>0.5193654688923917</v>
       </c>
+      <c r="G45">
+        <v>0.5193654688923917</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1150,6 +1287,9 @@
       <c r="F46">
         <v>0.3715220900853343</v>
       </c>
+      <c r="G46">
+        <v>0.3715220900853343</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1167,6 +1307,9 @@
       <c r="F47">
         <v>0.4151181668062128</v>
       </c>
+      <c r="G47">
+        <v>0.4151181668062128</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1184,6 +1327,9 @@
       <c r="F48">
         <v>1.558067608529416</v>
       </c>
+      <c r="G48">
+        <v>1.558067608529416</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1201,6 +1347,9 @@
       <c r="F49">
         <v>1.839264307407072</v>
       </c>
+      <c r="G49">
+        <v>1.839264307407072</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1218,6 +1367,9 @@
       <c r="F50">
         <v>2.291011113942119</v>
       </c>
+      <c r="G50">
+        <v>2.291011113942119</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1235,6 +1387,9 @@
       <c r="F51">
         <v>3.092988736506623</v>
       </c>
+      <c r="G51">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1252,6 +1407,9 @@
       <c r="F52">
         <v>-12.97390441953681</v>
       </c>
+      <c r="G52">
+        <v>-4</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1269,6 +1427,9 @@
       <c r="F53">
         <v>-1.008419499629548</v>
       </c>
+      <c r="G53">
+        <v>-1.008419499629548</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1286,6 +1447,9 @@
       <c r="F54">
         <v>-0.7901251409301253</v>
       </c>
+      <c r="G54">
+        <v>-0.7901251409301253</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1303,6 +1467,9 @@
       <c r="F55">
         <v>-0.7965740902790073</v>
       </c>
+      <c r="G55">
+        <v>-0.7965740902790073</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1320,6 +1487,9 @@
       <c r="F56">
         <v>-0.6726830641460991</v>
       </c>
+      <c r="G56">
+        <v>-0.6726830641460991</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1337,6 +1507,9 @@
       <c r="F57">
         <v>-0.1128752776697411</v>
       </c>
+      <c r="G57">
+        <v>-0.1128752776697411</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1354,6 +1527,9 @@
       <c r="F58">
         <v>-0.7714169047666857</v>
       </c>
+      <c r="G58">
+        <v>-0.7714169047666857</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1371,6 +1547,9 @@
       <c r="F59">
         <v>-0.6537218156934771</v>
       </c>
+      <c r="G59">
+        <v>-0.6537218156934771</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1388,6 +1567,9 @@
       <c r="F60">
         <v>-0.6919108518693734</v>
       </c>
+      <c r="G60">
+        <v>-0.6919108518693734</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1405,6 +1587,9 @@
       <c r="F61">
         <v>-0.6084113788557119</v>
       </c>
+      <c r="G61">
+        <v>-0.6084113788557119</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -1422,6 +1607,9 @@
       <c r="F62">
         <v>0.3694051289117799</v>
       </c>
+      <c r="G62">
+        <v>0.3694051289117799</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -1439,6 +1627,9 @@
       <c r="F63">
         <v>1.702929430544708</v>
       </c>
+      <c r="G63">
+        <v>1.702929430544708</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1456,6 +1647,9 @@
       <c r="F64">
         <v>2.179064269395877</v>
       </c>
+      <c r="G64">
+        <v>2.179064269395877</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -1473,6 +1667,9 @@
       <c r="F65">
         <v>3.041204567808126</v>
       </c>
+      <c r="G65">
+        <v>3.041204567808126</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -1490,6 +1687,9 @@
       <c r="F66">
         <v>3.092988736506623</v>
       </c>
+      <c r="G66">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -1507,6 +1707,9 @@
       <c r="F67">
         <v>0.2627826075289695</v>
       </c>
+      <c r="G67">
+        <v>0.2627826075289695</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -1524,6 +1727,9 @@
       <c r="F68">
         <v>0.7230402192798636</v>
       </c>
+      <c r="G68">
+        <v>0.7230402192798636</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -1541,6 +1747,9 @@
       <c r="F69">
         <v>0.7654939024244001</v>
       </c>
+      <c r="G69">
+        <v>0.7654939024244001</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -1558,6 +1767,9 @@
       <c r="F70">
         <v>0.6459848230862031</v>
       </c>
+      <c r="G70">
+        <v>0.6459848230862031</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -1575,6 +1787,9 @@
       <c r="F71">
         <v>0.5169030673428816</v>
       </c>
+      <c r="G71">
+        <v>0.5169030673428816</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -1592,6 +1807,9 @@
       <c r="F72">
         <v>-0.1502235474410901</v>
       </c>
+      <c r="G72">
+        <v>-0.1502235474410901</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -1609,6 +1827,9 @@
       <c r="F73">
         <v>-0.9229024837150683</v>
       </c>
+      <c r="G73">
+        <v>-0.9229024837150683</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -1626,6 +1847,9 @@
       <c r="F74">
         <v>-0.6297684259440216</v>
       </c>
+      <c r="G74">
+        <v>-0.6297684259440216</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -1643,6 +1867,9 @@
       <c r="F75">
         <v>-0.647263801966286</v>
       </c>
+      <c r="G75">
+        <v>-0.647263801966286</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -1660,6 +1887,9 @@
       <c r="F76">
         <v>-0.5706672465997678</v>
       </c>
+      <c r="G76">
+        <v>-0.5706672465997678</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -1677,6 +1907,9 @@
       <c r="F77">
         <v>-0.08876154549968482</v>
       </c>
+      <c r="G77">
+        <v>-0.08876154549968482</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -1694,6 +1927,9 @@
       <c r="F78">
         <v>-0.6624167582955319</v>
       </c>
+      <c r="G78">
+        <v>-0.6624167582955319</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -1711,6 +1947,9 @@
       <c r="F79">
         <v>-0.377951368011206</v>
       </c>
+      <c r="G79">
+        <v>-0.377951368011206</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -1728,6 +1967,9 @@
       <c r="F80">
         <v>-0.4092084980056591</v>
       </c>
+      <c r="G80">
+        <v>-0.4092084980056591</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -1745,6 +1987,9 @@
       <c r="F81">
         <v>-0.3891525954569753</v>
       </c>
+      <c r="G81">
+        <v>-0.3891525954569753</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -1762,6 +2007,9 @@
       <c r="F82">
         <v>-0.06450428773192897</v>
       </c>
+      <c r="G82">
+        <v>-0.06450428773192897</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -1779,6 +2027,9 @@
       <c r="F83">
         <v>-0.4281977102448243</v>
       </c>
+      <c r="G83">
+        <v>-0.4281977102448243</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -1796,6 +2047,9 @@
       <c r="F84">
         <v>-0.4954667056669593</v>
       </c>
+      <c r="G84">
+        <v>-0.4954667056669593</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -1813,6 +2067,9 @@
       <c r="F85">
         <v>-0.5232247059674168</v>
       </c>
+      <c r="G85">
+        <v>-0.5232247059674168</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -1830,6 +2087,9 @@
       <c r="F86">
         <v>-0.5130414710017455</v>
       </c>
+      <c r="G86">
+        <v>-0.5130414710017455</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -1847,6 +2107,9 @@
       <c r="F87">
         <v>-0.01260276454461589</v>
       </c>
+      <c r="G87">
+        <v>-0.01260276454461589</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -1864,6 +2127,9 @@
       <c r="F88">
         <v>-0.8380209049196554</v>
       </c>
+      <c r="G88">
+        <v>-0.8380209049196554</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -1881,6 +2147,9 @@
       <c r="F89">
         <v>-0.6762599020410228</v>
       </c>
+      <c r="G89">
+        <v>-0.6762599020410228</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -1898,6 +2167,9 @@
       <c r="F90">
         <v>-0.7144321304620028</v>
       </c>
+      <c r="G90">
+        <v>-0.7144321304620028</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -1915,6 +2187,9 @@
       <c r="F91">
         <v>-0.6220581849257982</v>
       </c>
+      <c r="G91">
+        <v>-0.6220581849257982</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -1932,6 +2207,9 @@
       <c r="F92">
         <v>-0.1548578737502189</v>
       </c>
+      <c r="G92">
+        <v>-0.1548578737502189</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -1949,6 +2227,9 @@
       <c r="F93">
         <v>-0.453676084429363</v>
       </c>
+      <c r="G93">
+        <v>-0.453676084429363</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -1966,6 +2247,9 @@
       <c r="F94">
         <v>-0.4075400632717903</v>
       </c>
+      <c r="G94">
+        <v>-0.4075400632717903</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -1983,6 +2267,9 @@
       <c r="F95">
         <v>-0.4789784707911243</v>
       </c>
+      <c r="G95">
+        <v>-0.4789784707911243</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -2000,6 +2287,9 @@
       <c r="F96">
         <v>-0.4810897151579744</v>
       </c>
+      <c r="G96">
+        <v>-0.4810897151579744</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -2017,6 +2307,9 @@
       <c r="F97">
         <v>0.4960309657139303</v>
       </c>
+      <c r="G97">
+        <v>0.4960309657139303</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -2034,6 +2327,9 @@
       <c r="F98">
         <v>-2.300644962222362</v>
       </c>
+      <c r="G98">
+        <v>-2.300644962222362</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -2051,6 +2347,9 @@
       <c r="F99">
         <v>1.634222947187799</v>
       </c>
+      <c r="G99">
+        <v>1.634222947187799</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -2068,6 +2367,9 @@
       <c r="F100">
         <v>-1.714896281201834</v>
       </c>
+      <c r="G100">
+        <v>-1.714896281201834</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -2085,6 +2387,9 @@
       <c r="F101">
         <v>0.7452638601652528</v>
       </c>
+      <c r="G101">
+        <v>0.7452638601652528</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -2102,6 +2407,9 @@
       <c r="F102">
         <v>-0.197888422742663</v>
       </c>
+      <c r="G102">
+        <v>-0.197888422742663</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -2119,6 +2427,9 @@
       <c r="F103">
         <v>-1.283874159486226</v>
       </c>
+      <c r="G103">
+        <v>-1.283874159486226</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -2136,6 +2447,9 @@
       <c r="F104">
         <v>-1.044400538061072</v>
       </c>
+      <c r="G104">
+        <v>-1.044400538061072</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -2153,6 +2467,9 @@
       <c r="F105">
         <v>-0.9402084256090271</v>
       </c>
+      <c r="G105">
+        <v>-0.9402084256090271</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -2170,6 +2487,9 @@
       <c r="F106">
         <v>-0.7713135799438052</v>
       </c>
+      <c r="G106">
+        <v>-0.7713135799438052</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -2187,6 +2507,9 @@
       <c r="F107">
         <v>0.209426409835506</v>
       </c>
+      <c r="G107">
+        <v>0.209426409835506</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -2204,6 +2527,9 @@
       <c r="F108">
         <v>0.1590489049788699</v>
       </c>
+      <c r="G108">
+        <v>0.1590489049788699</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -2221,6 +2547,9 @@
       <c r="F109">
         <v>0.08701066591897245</v>
       </c>
+      <c r="G109">
+        <v>0.08701066591897245</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -2238,6 +2567,9 @@
       <c r="F110">
         <v>-0.1039065262774629</v>
       </c>
+      <c r="G110">
+        <v>-0.1039065262774629</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -2255,6 +2587,9 @@
       <c r="F111">
         <v>-0.1974965823076505</v>
       </c>
+      <c r="G111">
+        <v>-0.1974965823076505</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -2272,6 +2607,9 @@
       <c r="F112">
         <v>0.5716952468610604</v>
       </c>
+      <c r="G112">
+        <v>0.5716952468610604</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -2289,6 +2627,9 @@
       <c r="F113">
         <v>2.398386728076275</v>
       </c>
+      <c r="G113">
+        <v>2.398386728076275</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -2306,6 +2647,9 @@
       <c r="F114">
         <v>2.835327240899685</v>
       </c>
+      <c r="G114">
+        <v>2.835327240899685</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -2323,6 +2667,9 @@
       <c r="F115">
         <v>4.465731974444721</v>
       </c>
+      <c r="G115">
+        <v>4</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -2340,6 +2687,9 @@
       <c r="F116">
         <v>3.092988736506623</v>
       </c>
+      <c r="G116">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -2357,6 +2707,9 @@
       <c r="F117">
         <v>0.802951770167828</v>
       </c>
+      <c r="G117">
+        <v>0.802951770167828</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -2374,6 +2727,9 @@
       <c r="F118">
         <v>-0.2192885229129949</v>
       </c>
+      <c r="G118">
+        <v>-0.2192885229129949</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -2391,6 +2747,9 @@
       <c r="F119">
         <v>-0.1429219571872713</v>
       </c>
+      <c r="G119">
+        <v>-0.1429219571872713</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -2408,6 +2767,9 @@
       <c r="F120">
         <v>-0.2881822616519916</v>
       </c>
+      <c r="G120">
+        <v>-0.2881822616519916</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -2425,6 +2787,9 @@
       <c r="F121">
         <v>-0.3310771872681869</v>
       </c>
+      <c r="G121">
+        <v>-0.3310771872681869</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -2442,6 +2807,9 @@
       <c r="F122">
         <v>-0.02704923143340335</v>
       </c>
+      <c r="G122">
+        <v>-0.02704923143340335</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -2459,6 +2827,9 @@
       <c r="F123">
         <v>-0.6119485271522831</v>
       </c>
+      <c r="G123">
+        <v>-0.6119485271522831</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -2476,6 +2847,9 @@
       <c r="F124">
         <v>-0.4594804568224359</v>
       </c>
+      <c r="G124">
+        <v>-0.4594804568224359</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -2493,6 +2867,9 @@
       <c r="F125">
         <v>-0.5387758156463933</v>
       </c>
+      <c r="G125">
+        <v>-0.5387758156463933</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -2510,6 +2887,9 @@
       <c r="F126">
         <v>-0.5060037004896057</v>
       </c>
+      <c r="G126">
+        <v>-0.5060037004896057</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -2527,6 +2907,9 @@
       <c r="F127">
         <v>0.005861166039954563</v>
       </c>
+      <c r="G127">
+        <v>0.005861166039954563</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -2544,6 +2927,9 @@
       <c r="F128">
         <v>-0.4083513328834523</v>
       </c>
+      <c r="G128">
+        <v>-0.4083513328834523</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -2561,6 +2947,9 @@
       <c r="F129">
         <v>-0.2908220183064332</v>
       </c>
+      <c r="G129">
+        <v>-0.2908220183064332</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -2578,6 +2967,9 @@
       <c r="F130">
         <v>-0.404124319278871</v>
       </c>
+      <c r="G130">
+        <v>-0.404124319278871</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -2595,6 +2987,9 @@
       <c r="F131">
         <v>-0.4146765500937585</v>
       </c>
+      <c r="G131">
+        <v>-0.4146765500937585</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -2612,6 +3007,9 @@
       <c r="F132">
         <v>-0.3894122259319928</v>
       </c>
+      <c r="G132">
+        <v>-0.3894122259319928</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -2629,6 +3027,9 @@
       <c r="F133">
         <v>-1.473312388861624</v>
       </c>
+      <c r="G133">
+        <v>-1.473312388861624</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -2646,6 +3047,9 @@
       <c r="F134">
         <v>-0.8369972438821899</v>
       </c>
+      <c r="G134">
+        <v>-0.8369972438821899</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -2663,6 +3067,9 @@
       <c r="F135">
         <v>-0.6963416668324039</v>
       </c>
+      <c r="G135">
+        <v>-0.6963416668324039</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -2680,6 +3087,9 @@
       <c r="F136">
         <v>-0.5533843503143291</v>
       </c>
+      <c r="G136">
+        <v>-0.5533843503143291</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -2697,6 +3107,9 @@
       <c r="F137">
         <v>-0.0373963395749853</v>
       </c>
+      <c r="G137">
+        <v>-0.0373963395749853</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -2714,6 +3127,9 @@
       <c r="F138">
         <v>-0.4484803912120979</v>
       </c>
+      <c r="G138">
+        <v>-0.4484803912120979</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -2731,6 +3147,9 @@
       <c r="F139">
         <v>-0.2909569686633067</v>
       </c>
+      <c r="G139">
+        <v>-0.2909569686633067</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -2748,6 +3167,9 @@
       <c r="F140">
         <v>-0.397164454613569</v>
       </c>
+      <c r="G140">
+        <v>-0.397164454613569</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -2765,6 +3187,9 @@
       <c r="F141">
         <v>-0.4085012882157534</v>
       </c>
+      <c r="G141">
+        <v>-0.4085012882157534</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -2782,6 +3207,9 @@
       <c r="F142">
         <v>-0.2909129114858719</v>
       </c>
+      <c r="G142">
+        <v>-0.2909129114858719</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -2799,6 +3227,9 @@
       <c r="F143">
         <v>0.2799675292913701</v>
       </c>
+      <c r="G143">
+        <v>0.2799675292913701</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -2816,6 +3247,9 @@
       <c r="F144">
         <v>-0.5679098009762198</v>
       </c>
+      <c r="G144">
+        <v>-0.5679098009762198</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -2833,6 +3267,9 @@
       <c r="F145">
         <v>-0.2975087425851662</v>
       </c>
+      <c r="G145">
+        <v>-0.2975087425851662</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -2850,6 +3287,9 @@
       <c r="F146">
         <v>-0.4525739851519948</v>
       </c>
+      <c r="G146">
+        <v>-0.4525739851519948</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -2867,6 +3307,9 @@
       <c r="F147">
         <v>-0.03634686018980464</v>
       </c>
+      <c r="G147">
+        <v>-0.03634686018980464</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -2884,6 +3327,9 @@
       <c r="F148">
         <v>0.2041290737198342</v>
       </c>
+      <c r="G148">
+        <v>0.2041290737198342</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -2901,6 +3347,9 @@
       <c r="F149">
         <v>-0.2086543051337568</v>
       </c>
+      <c r="G149">
+        <v>-0.2086543051337568</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -2918,6 +3367,9 @@
       <c r="F150">
         <v>-0.1458775110429163</v>
       </c>
+      <c r="G150">
+        <v>-0.1458775110429163</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -2935,6 +3387,9 @@
       <c r="F151">
         <v>-0.2978051033863632</v>
       </c>
+      <c r="G151">
+        <v>-0.2978051033863632</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -2952,6 +3407,9 @@
       <c r="F152">
         <v>0.1353509160874147</v>
       </c>
+      <c r="G152">
+        <v>0.1353509160874147</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -2969,6 +3427,9 @@
       <c r="F153">
         <v>-0.8888198169940641</v>
       </c>
+      <c r="G153">
+        <v>-0.8888198169940641</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -2986,6 +3447,9 @@
       <c r="F154">
         <v>-0.170833775451254</v>
       </c>
+      <c r="G154">
+        <v>-0.170833775451254</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -3003,6 +3467,9 @@
       <c r="F155">
         <v>-0.6106438007981072</v>
       </c>
+      <c r="G155">
+        <v>-0.6106438007981072</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -3020,6 +3487,9 @@
       <c r="F156">
         <v>-0.4192428447356354</v>
       </c>
+      <c r="G156">
+        <v>-0.4192428447356354</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -3037,6 +3507,9 @@
       <c r="F157">
         <v>0.9301100947860557</v>
       </c>
+      <c r="G157">
+        <v>0.9301100947860557</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -3054,6 +3527,9 @@
       <c r="F158">
         <v>1.921561013795578</v>
       </c>
+      <c r="G158">
+        <v>1.921561013795578</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -3071,6 +3547,9 @@
       <c r="F159">
         <v>2.574900941708078</v>
       </c>
+      <c r="G159">
+        <v>2.574900941708078</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -3088,6 +3567,9 @@
       <c r="F160">
         <v>4.074596258935308</v>
       </c>
+      <c r="G160">
+        <v>4</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -3105,6 +3587,9 @@
       <c r="F161">
         <v>3.092988736506623</v>
       </c>
+      <c r="G161">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -3122,6 +3607,9 @@
       <c r="F162">
         <v>0.08759847913225996</v>
       </c>
+      <c r="G162">
+        <v>0.08759847913225996</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -3139,6 +3627,9 @@
       <c r="F163">
         <v>-0.05863389791672658</v>
       </c>
+      <c r="G163">
+        <v>-0.05863389791672658</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -3156,6 +3647,9 @@
       <c r="F164">
         <v>-0.007684820108826223</v>
       </c>
+      <c r="G164">
+        <v>-0.007684820108826223</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -3173,6 +3667,9 @@
       <c r="F165">
         <v>-0.1622597078420971</v>
       </c>
+      <c r="G165">
+        <v>-0.1622597078420971</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -3190,6 +3687,9 @@
       <c r="F166">
         <v>-0.2366333493849686</v>
       </c>
+      <c r="G166">
+        <v>-0.2366333493849686</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -3207,6 +3707,9 @@
       <c r="F167">
         <v>0.08259029385123365</v>
       </c>
+      <c r="G167">
+        <v>0.08259029385123365</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -3224,6 +3727,9 @@
       <c r="F168">
         <v>-0.7862889029711996</v>
       </c>
+      <c r="G168">
+        <v>-0.7862889029711996</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -3241,6 +3747,9 @@
       <c r="F169">
         <v>-0.2072839709449317</v>
       </c>
+      <c r="G169">
+        <v>-0.2072839709449317</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -3258,6 +3767,9 @@
       <c r="F170">
         <v>-0.6396059973776792</v>
       </c>
+      <c r="G170">
+        <v>-0.6396059973776792</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -3275,6 +3787,9 @@
       <c r="F171">
         <v>-0.4036727141748028</v>
       </c>
+      <c r="G171">
+        <v>-0.4036727141748028</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -3292,6 +3807,9 @@
       <c r="F172">
         <v>-0.08935435510142625</v>
       </c>
+      <c r="G172">
+        <v>-0.08935435510142625</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -3309,6 +3827,9 @@
       <c r="F173">
         <v>-0.9343584553901741</v>
       </c>
+      <c r="G173">
+        <v>-0.9343584553901741</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -3326,6 +3847,9 @@
       <c r="F174">
         <v>-0.7333114257257408</v>
       </c>
+      <c r="G174">
+        <v>-0.7333114257257408</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -3343,6 +3867,9 @@
       <c r="F175">
         <v>-0.7554184764471201</v>
       </c>
+      <c r="G175">
+        <v>-0.7554184764471201</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -3360,6 +3887,9 @@
       <c r="F176">
         <v>-0.6474836886544372</v>
       </c>
+      <c r="G176">
+        <v>-0.6474836886544372</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -3377,6 +3907,9 @@
       <c r="F177">
         <v>0.1025366602975421</v>
       </c>
+      <c r="G177">
+        <v>0.1025366602975421</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -3394,6 +3927,9 @@
       <c r="F178">
         <v>0.1389453603839934</v>
       </c>
+      <c r="G178">
+        <v>0.1389453603839934</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -3411,6 +3947,9 @@
       <c r="F179">
         <v>-0.02476869890216862</v>
       </c>
+      <c r="G179">
+        <v>-0.02476869890216862</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -3428,6 +3967,9 @@
       <c r="F180">
         <v>-0.1266060852305862</v>
       </c>
+      <c r="G180">
+        <v>-0.1266060852305862</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -3445,6 +3987,9 @@
       <c r="F181">
         <v>-0.04175913516884931</v>
       </c>
+      <c r="G181">
+        <v>-0.04175913516884931</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -3462,6 +4007,9 @@
       <c r="F182">
         <v>0.07935442392775564</v>
       </c>
+      <c r="G182">
+        <v>0.07935442392775564</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -3479,6 +4027,9 @@
       <c r="F183">
         <v>-0.2529859559079446</v>
       </c>
+      <c r="G183">
+        <v>-0.2529859559079446</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -3496,6 +4047,9 @@
       <c r="F184">
         <v>-0.2285262417358057</v>
       </c>
+      <c r="G184">
+        <v>-0.2285262417358057</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -3513,6 +4067,9 @@
       <c r="F185">
         <v>-0.3401069120901829</v>
       </c>
+      <c r="G185">
+        <v>-0.3401069120901829</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -3530,6 +4087,9 @@
       <c r="F186">
         <v>1.180392780653813</v>
       </c>
+      <c r="G186">
+        <v>1.180392780653813</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -3547,6 +4107,9 @@
       <c r="F187">
         <v>0.725387442107933</v>
       </c>
+      <c r="G187">
+        <v>0.725387442107933</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -3564,6 +4127,9 @@
       <c r="F188">
         <v>0.8309887438085566</v>
       </c>
+      <c r="G188">
+        <v>0.8309887438085566</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -3581,6 +4147,9 @@
       <c r="F189">
         <v>0.7327839191802538</v>
       </c>
+      <c r="G189">
+        <v>0.7327839191802538</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -3598,6 +4167,9 @@
       <c r="F190">
         <v>0.6191461751940059</v>
       </c>
+      <c r="G190">
+        <v>0.6191461751940059</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -3615,6 +4187,9 @@
       <c r="F191">
         <v>-0.5595471025078504</v>
       </c>
+      <c r="G191">
+        <v>-0.5595471025078504</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -3632,6 +4207,9 @@
       <c r="F192">
         <v>0.5015183477092717</v>
       </c>
+      <c r="G192">
+        <v>0.5015183477092717</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -3649,6 +4227,9 @@
       <c r="F193">
         <v>-1.536813945281128</v>
       </c>
+      <c r="G193">
+        <v>-1.536813945281128</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -3666,6 +4247,9 @@
       <c r="F194">
         <v>-0.2322286698649069</v>
       </c>
+      <c r="G194">
+        <v>-0.2322286698649069</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -3683,6 +4267,9 @@
       <c r="F195">
         <v>-0.8373551492089075</v>
       </c>
+      <c r="G195">
+        <v>-0.8373551492089075</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -3700,6 +4287,9 @@
       <c r="F196">
         <v>0.3548512146266568</v>
       </c>
+      <c r="G196">
+        <v>0.3548512146266568</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -3717,6 +4307,9 @@
       <c r="F197">
         <v>1.541684096755897</v>
       </c>
+      <c r="G197">
+        <v>1.541684096755897</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -3734,6 +4327,9 @@
       <c r="F198">
         <v>1.922252883773254</v>
       </c>
+      <c r="G198">
+        <v>1.922252883773254</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -3751,6 +4347,9 @@
       <c r="F199">
         <v>2.479987564472851</v>
       </c>
+      <c r="G199">
+        <v>2.479987564472851</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -3768,6 +4367,9 @@
       <c r="F200">
         <v>3.092988736506623</v>
       </c>
+      <c r="G200">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -3785,6 +4387,9 @@
       <c r="F201">
         <v>-0.002522127769361928</v>
       </c>
+      <c r="G201">
+        <v>-0.002522127769361928</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -3802,6 +4407,9 @@
       <c r="F202">
         <v>-0.641394661749605</v>
       </c>
+      <c r="G202">
+        <v>-0.641394661749605</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -3819,6 +4427,9 @@
       <c r="F203">
         <v>-0.5214222588405683</v>
       </c>
+      <c r="G203">
+        <v>-0.5214222588405683</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -3836,6 +4447,9 @@
       <c r="F204">
         <v>-0.5980302407214141</v>
       </c>
+      <c r="G204">
+        <v>-0.5980302407214141</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -3853,6 +4467,9 @@
       <c r="F205">
         <v>-0.5477882559488156</v>
       </c>
+      <c r="G205">
+        <v>-0.5477882559488156</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -3870,6 +4487,9 @@
       <c r="F206">
         <v>-0.1993286849037745</v>
       </c>
+      <c r="G206">
+        <v>-0.1993286849037745</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -3887,6 +4507,9 @@
       <c r="F207">
         <v>-0.7788067951136748</v>
       </c>
+      <c r="G207">
+        <v>-0.7788067951136748</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -3904,6 +4527,9 @@
       <c r="F208">
         <v>-0.788985721428521</v>
       </c>
+      <c r="G208">
+        <v>-0.788985721428521</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -3921,6 +4547,9 @@
       <c r="F209">
         <v>-0.7522057720800257</v>
       </c>
+      <c r="G209">
+        <v>-0.7522057720800257</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -3938,6 +4567,9 @@
       <c r="F210">
         <v>-0.6550528659991882</v>
       </c>
+      <c r="G210">
+        <v>-0.6550528659991882</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -3955,6 +4587,9 @@
       <c r="F211">
         <v>0.00454889430247201</v>
       </c>
+      <c r="G211">
+        <v>0.00454889430247201</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -3972,6 +4607,9 @@
       <c r="F212">
         <v>-3.310396645997412</v>
       </c>
+      <c r="G212">
+        <v>-3.310396645997412</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -3989,6 +4627,9 @@
       <c r="F213">
         <v>0.01639596696438553</v>
       </c>
+      <c r="G213">
+        <v>0.01639596696438553</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -4006,6 +4647,9 @@
       <c r="F214">
         <v>0.009222974974733802</v>
       </c>
+      <c r="G214">
+        <v>0.009222974974733802</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215">
@@ -4023,6 +4667,9 @@
       <c r="F215">
         <v>-1.446408757973947</v>
       </c>
+      <c r="G215">
+        <v>-1.446408757973947</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -4040,6 +4687,9 @@
       <c r="F216">
         <v>0.1412057071261358</v>
       </c>
+      <c r="G216">
+        <v>0.1412057071261358</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217">
@@ -4057,6 +4707,9 @@
       <c r="F217">
         <v>0.7757381894554863</v>
       </c>
+      <c r="G217">
+        <v>0.7757381894554863</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -4074,6 +4727,9 @@
       <c r="F218">
         <v>0.4747240128274326</v>
       </c>
+      <c r="G218">
+        <v>0.4747240128274326</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -4091,6 +4747,9 @@
       <c r="F219">
         <v>0.5539830053920807</v>
       </c>
+      <c r="G219">
+        <v>0.5539830053920807</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220">
@@ -4108,6 +4767,9 @@
       <c r="F220">
         <v>0.2921646505296067</v>
       </c>
+      <c r="G220">
+        <v>0.2921646505296067</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -4125,6 +4787,9 @@
       <c r="F221">
         <v>0.02617022206478183</v>
       </c>
+      <c r="G221">
+        <v>0.02617022206478183</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -4142,6 +4807,9 @@
       <c r="F222">
         <v>-0.2714357087755848</v>
       </c>
+      <c r="G222">
+        <v>-0.2714357087755848</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -4159,6 +4827,9 @@
       <c r="F223">
         <v>-0.1330456549895072</v>
       </c>
+      <c r="G223">
+        <v>-0.1330456549895072</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -4176,6 +4847,9 @@
       <c r="F224">
         <v>-0.2484302569758157</v>
       </c>
+      <c r="G224">
+        <v>-0.2484302569758157</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -4193,6 +4867,9 @@
       <c r="F225">
         <v>-0.2939528303477846</v>
       </c>
+      <c r="G225">
+        <v>-0.2939528303477846</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -4210,6 +4887,9 @@
       <c r="F226">
         <v>-0.031027793951914</v>
       </c>
+      <c r="G226">
+        <v>-0.031027793951914</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -4227,6 +4907,9 @@
       <c r="F227">
         <v>-0.7331111769541893</v>
       </c>
+      <c r="G227">
+        <v>-0.7331111769541893</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -4244,6 +4927,9 @@
       <c r="F228">
         <v>-0.5843745212143977</v>
       </c>
+      <c r="G228">
+        <v>-0.5843745212143977</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -4261,6 +4947,9 @@
       <c r="F229">
         <v>-0.644759318731258</v>
       </c>
+      <c r="G229">
+        <v>-0.644759318731258</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230">
@@ -4278,6 +4967,9 @@
       <c r="F230">
         <v>-0.5778237060104935</v>
       </c>
+      <c r="G230">
+        <v>-0.5778237060104935</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231">
@@ -4295,6 +4987,9 @@
       <c r="F231">
         <v>-0.08488808986898223</v>
       </c>
+      <c r="G231">
+        <v>-0.08488808986898223</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232">
@@ -4312,6 +5007,9 @@
       <c r="F232">
         <v>-0.7792648674812075</v>
       </c>
+      <c r="G232">
+        <v>-0.7792648674812075</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233">
@@ -4329,6 +5027,9 @@
       <c r="F233">
         <v>-0.6695227354173874</v>
       </c>
+      <c r="G233">
+        <v>-0.6695227354173874</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234">
@@ -4346,6 +5047,9 @@
       <c r="F234">
         <v>-0.6954710747349376</v>
       </c>
+      <c r="G234">
+        <v>-0.6954710747349376</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235">
@@ -4363,6 +5067,9 @@
       <c r="F235">
         <v>-0.6131133435661399</v>
       </c>
+      <c r="G235">
+        <v>-0.6131133435661399</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236">
@@ -4380,6 +5087,9 @@
       <c r="F236">
         <v>0.02900135590653283</v>
       </c>
+      <c r="G236">
+        <v>0.02900135590653283</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237">
@@ -4397,6 +5107,9 @@
       <c r="F237">
         <v>0.04466644110651434</v>
       </c>
+      <c r="G237">
+        <v>0.04466644110651434</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238">
@@ -4414,6 +5127,9 @@
       <c r="F238">
         <v>-0.07197974989615472</v>
       </c>
+      <c r="G238">
+        <v>-0.07197974989615472</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239">
@@ -4431,6 +5147,9 @@
       <c r="F239">
         <v>-0.1721926161656105</v>
       </c>
+      <c r="G239">
+        <v>-0.1721926161656105</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240">
@@ -4448,6 +5167,9 @@
       <c r="F240">
         <v>-0.2571567505450357</v>
       </c>
+      <c r="G240">
+        <v>-0.2571567505450357</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241">
@@ -4465,6 +5187,9 @@
       <c r="F241">
         <v>-0.2997684057196634</v>
       </c>
+      <c r="G241">
+        <v>-0.2997684057196634</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -4482,6 +5207,9 @@
       <c r="F242">
         <v>-0.4733811660839622</v>
       </c>
+      <c r="G242">
+        <v>-0.4733811660839622</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -4499,6 +5227,9 @@
       <c r="F243">
         <v>-0.935047677044045</v>
       </c>
+      <c r="G243">
+        <v>-0.935047677044045</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244">
@@ -4516,6 +5247,9 @@
       <c r="F244">
         <v>-0.679382723584139</v>
       </c>
+      <c r="G244">
+        <v>-0.679382723584139</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245">
@@ -4533,6 +5267,9 @@
       <c r="F245">
         <v>-0.6754427972741315</v>
       </c>
+      <c r="G245">
+        <v>-0.6754427972741315</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246">
@@ -4550,6 +5287,9 @@
       <c r="F246">
         <v>-0.06983604369187839</v>
       </c>
+      <c r="G246">
+        <v>-0.06983604369187839</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247">
@@ -4567,6 +5307,9 @@
       <c r="F247">
         <v>-0.8013315873160465</v>
       </c>
+      <c r="G247">
+        <v>-0.8013315873160465</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248">
@@ -4584,6 +5327,9 @@
       <c r="F248">
         <v>-0.6249871754879622</v>
       </c>
+      <c r="G248">
+        <v>-0.6249871754879622</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249">
@@ -4601,6 +5347,9 @@
       <c r="F249">
         <v>-0.6740608696080307</v>
       </c>
+      <c r="G249">
+        <v>-0.6740608696080307</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250">
@@ -4618,6 +5367,9 @@
       <c r="F250">
         <v>-0.5964066129108132</v>
       </c>
+      <c r="G250">
+        <v>-0.5964066129108132</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251">
@@ -4635,6 +5387,9 @@
       <c r="F251">
         <v>-0.05683854216725399</v>
       </c>
+      <c r="G251">
+        <v>-0.05683854216725399</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252">
@@ -4652,6 +5407,9 @@
       <c r="F252">
         <v>-0.886245540981541</v>
       </c>
+      <c r="G252">
+        <v>-0.886245540981541</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253">
@@ -4669,6 +5427,9 @@
       <c r="F253">
         <v>-0.6906212445096443</v>
       </c>
+      <c r="G253">
+        <v>-0.6906212445096443</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254">
@@ -4686,6 +5447,9 @@
       <c r="F254">
         <v>-0.7264719465024246</v>
       </c>
+      <c r="G254">
+        <v>-0.7264719465024246</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255">
@@ -4703,6 +5467,9 @@
       <c r="F255">
         <v>-0.6291638647252956</v>
       </c>
+      <c r="G255">
+        <v>-0.6291638647252956</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256">
@@ -4720,6 +5487,9 @@
       <c r="F256">
         <v>0.1119325488862771</v>
       </c>
+      <c r="G256">
+        <v>0.1119325488862771</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257">
@@ -4737,6 +5507,9 @@
       <c r="F257">
         <v>0.3056337884644749</v>
       </c>
+      <c r="G257">
+        <v>0.3056337884644749</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258">
@@ -4754,6 +5527,9 @@
       <c r="F258">
         <v>0.3476555352288731</v>
       </c>
+      <c r="G258">
+        <v>0.3476555352288731</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259">
@@ -4771,6 +5547,9 @@
       <c r="F259">
         <v>0.185697493925271</v>
       </c>
+      <c r="G259">
+        <v>0.185697493925271</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260">
@@ -4788,6 +5567,9 @@
       <c r="F260">
         <v>0.05532592483124567</v>
       </c>
+      <c r="G260">
+        <v>0.05532592483124567</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261">
@@ -4805,6 +5587,9 @@
       <c r="F261">
         <v>-0.05418938937827188</v>
       </c>
+      <c r="G261">
+        <v>-0.05418938937827188</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262">
@@ -4822,6 +5607,9 @@
       <c r="F262">
         <v>-0.8238155200301597</v>
       </c>
+      <c r="G262">
+        <v>-0.8238155200301597</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263">
@@ -4839,6 +5627,9 @@
       <c r="F263">
         <v>-0.6536664724230895</v>
       </c>
+      <c r="G263">
+        <v>-0.6536664724230895</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264">
@@ -4856,6 +5647,9 @@
       <c r="F264">
         <v>-0.6969565542862639</v>
       </c>
+      <c r="G264">
+        <v>-0.6969565542862639</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265">
@@ -4873,6 +5667,9 @@
       <c r="F265">
         <v>-0.6110454672402043</v>
       </c>
+      <c r="G265">
+        <v>-0.6110454672402043</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266">
@@ -4890,6 +5687,9 @@
       <c r="F266">
         <v>0.1333196367556268</v>
       </c>
+      <c r="G266">
+        <v>0.1333196367556268</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267">
@@ -4907,6 +5707,9 @@
       <c r="F267">
         <v>-0.8445187954831989</v>
       </c>
+      <c r="G267">
+        <v>-0.8445187954831989</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268">
@@ -4924,6 +5727,9 @@
       <c r="F268">
         <v>-0.26935772692817</v>
       </c>
+      <c r="G268">
+        <v>-0.26935772692817</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269">
@@ -4941,6 +5747,9 @@
       <c r="F269">
         <v>-0.5698920611862075</v>
       </c>
+      <c r="G269">
+        <v>-0.5698920611862075</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270">
@@ -4958,6 +5767,9 @@
       <c r="F270">
         <v>-0.4650940725953209</v>
       </c>
+      <c r="G270">
+        <v>-0.4650940725953209</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271">
@@ -4975,6 +5787,9 @@
       <c r="F271">
         <v>-0.3698991122879996</v>
       </c>
+      <c r="G271">
+        <v>-0.3698991122879996</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272">
@@ -4992,6 +5807,9 @@
       <c r="F272">
         <v>-0.7485396426097174</v>
       </c>
+      <c r="G272">
+        <v>-0.7485396426097174</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273">
@@ -5009,6 +5827,9 @@
       <c r="F273">
         <v>-0.6060676420784809</v>
       </c>
+      <c r="G273">
+        <v>-0.6060676420784809</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274">
@@ -5026,6 +5847,9 @@
       <c r="F274">
         <v>-0.6581623199835613</v>
       </c>
+      <c r="G274">
+        <v>-0.6581623199835613</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275">
@@ -5043,6 +5867,9 @@
       <c r="F275">
         <v>-0.5872244565315573</v>
       </c>
+      <c r="G275">
+        <v>-0.5872244565315573</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276">
@@ -5060,6 +5887,9 @@
       <c r="F276">
         <v>-0.605468098048607</v>
       </c>
+      <c r="G276">
+        <v>-0.605468098048607</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277">
@@ -5077,6 +5907,9 @@
       <c r="F277">
         <v>-0.1683280405329313</v>
       </c>
+      <c r="G277">
+        <v>-0.1683280405329313</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278">
@@ -5094,6 +5927,9 @@
       <c r="F278">
         <v>-0.9541806000324334</v>
       </c>
+      <c r="G278">
+        <v>-0.9541806000324334</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279">
@@ -5111,6 +5947,9 @@
       <c r="F279">
         <v>-0.6622455544967722</v>
       </c>
+      <c r="G279">
+        <v>-0.6622455544967722</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280">
@@ -5128,6 +5967,9 @@
       <c r="F280">
         <v>-0.6543513535638344</v>
       </c>
+      <c r="G280">
+        <v>-0.6543513535638344</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281">
@@ -5145,6 +5987,9 @@
       <c r="F281">
         <v>-0.5104844169758641</v>
       </c>
+      <c r="G281">
+        <v>-0.5104844169758641</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282">
@@ -5162,6 +6007,9 @@
       <c r="F282">
         <v>0.1726424194185125</v>
       </c>
+      <c r="G282">
+        <v>0.1726424194185125</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283">
@@ -5179,6 +6027,9 @@
       <c r="F283">
         <v>-2.095777030013303</v>
       </c>
+      <c r="G283">
+        <v>-2.095777030013303</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284">
@@ -5196,6 +6047,9 @@
       <c r="F284">
         <v>-0.1143388798853761</v>
       </c>
+      <c r="G284">
+        <v>-0.1143388798853761</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285">
@@ -5213,6 +6067,9 @@
       <c r="F285">
         <v>-1.271368213266615</v>
       </c>
+      <c r="G285">
+        <v>-1.271368213266615</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286">
@@ -5230,6 +6087,9 @@
       <c r="F286">
         <v>0.2121602832537191</v>
       </c>
+      <c r="G286">
+        <v>0.2121602832537191</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287">
@@ -5247,6 +6107,9 @@
       <c r="F287">
         <v>0.7838674389272173</v>
       </c>
+      <c r="G287">
+        <v>0.7838674389272173</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288">
@@ -5264,6 +6127,9 @@
       <c r="F288">
         <v>0.8158925272593014</v>
       </c>
+      <c r="G288">
+        <v>0.8158925272593014</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289">
@@ -5281,6 +6147,9 @@
       <c r="F289">
         <v>0.7367183231788199</v>
       </c>
+      <c r="G289">
+        <v>0.7367183231788199</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290">
@@ -5298,6 +6167,9 @@
       <c r="F290">
         <v>0.6181081260810434</v>
       </c>
+      <c r="G290">
+        <v>0.6181081260810434</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291">
@@ -5315,6 +6187,9 @@
       <c r="F291">
         <v>0.01619818133306477</v>
       </c>
+      <c r="G291">
+        <v>0.01619818133306477</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292">
@@ -5332,6 +6207,9 @@
       <c r="F292">
         <v>-1.897249508038879</v>
       </c>
+      <c r="G292">
+        <v>-1.897249508038879</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293">
@@ -5349,6 +6227,9 @@
       <c r="F293">
         <v>-0.4373282402110962</v>
       </c>
+      <c r="G293">
+        <v>-0.4373282402110962</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294">
@@ -5366,6 +6247,9 @@
       <c r="F294">
         <v>-1.249261330884603</v>
       </c>
+      <c r="G294">
+        <v>-1.249261330884603</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295">
@@ -5383,6 +6267,9 @@
       <c r="F295">
         <v>-0.5153360670344571</v>
       </c>
+      <c r="G295">
+        <v>-0.5153360670344571</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296">
@@ -5400,6 +6287,9 @@
       <c r="F296">
         <v>0.06493181601941678</v>
       </c>
+      <c r="G296">
+        <v>0.06493181601941678</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297">
@@ -5417,6 +6307,9 @@
       <c r="F297">
         <v>-0.02851532847152145</v>
       </c>
+      <c r="G297">
+        <v>-0.02851532847152145</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298">
@@ -5434,6 +6327,9 @@
       <c r="F298">
         <v>-0.08152106114773383</v>
       </c>
+      <c r="G298">
+        <v>-0.08152106114773383</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299">
@@ -5451,6 +6347,9 @@
       <c r="F299">
         <v>-0.1904390865543121</v>
       </c>
+      <c r="G299">
+        <v>-0.1904390865543121</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300">
@@ -5468,6 +6367,9 @@
       <c r="F300">
         <v>-0.2716557496548639</v>
       </c>
+      <c r="G300">
+        <v>-0.2716557496548639</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301">
@@ -5485,6 +6387,9 @@
       <c r="F301">
         <v>0.003037503347529465</v>
       </c>
+      <c r="G301">
+        <v>0.003037503347529465</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302">
@@ -5502,6 +6407,9 @@
       <c r="F302">
         <v>-0.02049398053724908</v>
       </c>
+      <c r="G302">
+        <v>-0.02049398053724908</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303">
@@ -5519,6 +6427,9 @@
       <c r="F303">
         <v>-0.09531123041909723</v>
       </c>
+      <c r="G303">
+        <v>-0.09531123041909723</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304">
@@ -5536,6 +6447,9 @@
       <c r="F304">
         <v>-0.2168346609918256</v>
       </c>
+      <c r="G304">
+        <v>-0.2168346609918256</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305">
@@ -5553,6 +6467,9 @@
       <c r="F305">
         <v>-0.2830423022464288</v>
       </c>
+      <c r="G305">
+        <v>-0.2830423022464288</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306">
@@ -5570,6 +6487,9 @@
       <c r="F306">
         <v>-0.3703687349306549</v>
       </c>
+      <c r="G306">
+        <v>-0.3703687349306549</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307">
@@ -5587,6 +6507,9 @@
       <c r="F307">
         <v>-0.2994824282451445</v>
       </c>
+      <c r="G307">
+        <v>-0.2994824282451445</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308">
@@ -5604,6 +6527,9 @@
       <c r="F308">
         <v>-0.9158693018016059</v>
       </c>
+      <c r="G308">
+        <v>-0.9158693018016059</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309">
@@ -5621,6 +6547,9 @@
       <c r="F309">
         <v>-0.6373740465188875</v>
       </c>
+      <c r="G309">
+        <v>-0.6373740465188875</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310">
@@ -5638,6 +6567,9 @@
       <c r="F310">
         <v>-0.6521276045496718</v>
       </c>
+      <c r="G310">
+        <v>-0.6521276045496718</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311">
@@ -5655,6 +6587,9 @@
       <c r="F311">
         <v>0.154044412428689</v>
       </c>
+      <c r="G311">
+        <v>0.154044412428689</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312">
@@ -5672,6 +6607,9 @@
       <c r="F312">
         <v>0.7753124040770406</v>
       </c>
+      <c r="G312">
+        <v>0.7753124040770406</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313">
@@ -5689,6 +6627,9 @@
       <c r="F313">
         <v>0.7993881906060916</v>
       </c>
+      <c r="G313">
+        <v>0.7993881906060916</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314">
@@ -5706,6 +6647,9 @@
       <c r="F314">
         <v>0.7060573916572948</v>
       </c>
+      <c r="G314">
+        <v>0.7060573916572948</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315">
@@ -5723,6 +6667,9 @@
       <c r="F315">
         <v>0.5864175081808553</v>
       </c>
+      <c r="G315">
+        <v>0.5864175081808553</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316">
@@ -5740,6 +6687,9 @@
       <c r="F316">
         <v>0.06317009629148605</v>
       </c>
+      <c r="G316">
+        <v>0.06317009629148605</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317">
@@ -5757,6 +6707,9 @@
       <c r="F317">
         <v>-0.2375062020256162</v>
       </c>
+      <c r="G317">
+        <v>-0.2375062020256162</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318">
@@ -5774,6 +6727,9 @@
       <c r="F318">
         <v>-0.1774697877450091</v>
       </c>
+      <c r="G318">
+        <v>-0.1774697877450091</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319">
@@ -5791,6 +6747,9 @@
       <c r="F319">
         <v>-0.3137479846178754</v>
       </c>
+      <c r="G319">
+        <v>-0.3137479846178754</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320">
@@ -5808,6 +6767,9 @@
       <c r="F320">
         <v>-0.3509175418103536</v>
       </c>
+      <c r="G320">
+        <v>-0.3509175418103536</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321">
@@ -5825,6 +6787,9 @@
       <c r="F321">
         <v>0.2457970927394151</v>
       </c>
+      <c r="G321">
+        <v>0.2457970927394151</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322">
@@ -5842,6 +6807,9 @@
       <c r="F322">
         <v>1.310269695923392</v>
       </c>
+      <c r="G322">
+        <v>1.310269695923392</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323">
@@ -5859,6 +6827,9 @@
       <c r="F323">
         <v>1.49358273476466</v>
       </c>
+      <c r="G323">
+        <v>1.49358273476466</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324">
@@ -5876,6 +6847,9 @@
       <c r="F324">
         <v>1.7037248288792</v>
       </c>
+      <c r="G324">
+        <v>1.7037248288792</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325">
@@ -5893,6 +6867,9 @@
       <c r="F325">
         <v>2.130833126162919</v>
       </c>
+      <c r="G325">
+        <v>2.130833126162919</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326">
@@ -5910,6 +6887,9 @@
       <c r="F326">
         <v>-0.6601792507105382</v>
       </c>
+      <c r="G326">
+        <v>-0.6601792507105382</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327">
@@ -5927,6 +6907,9 @@
       <c r="F327">
         <v>-0.8374390403589108</v>
       </c>
+      <c r="G327">
+        <v>-0.8374390403589108</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328">
@@ -5944,6 +6927,9 @@
       <c r="F328">
         <v>-0.8071168571474305</v>
       </c>
+      <c r="G328">
+        <v>-0.8071168571474305</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329">
@@ -5961,6 +6947,9 @@
       <c r="F329">
         <v>-0.7401542189561854</v>
       </c>
+      <c r="G329">
+        <v>-0.7401542189561854</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330">
@@ -5978,6 +6967,9 @@
       <c r="F330">
         <v>-0.6661795418934083</v>
       </c>
+      <c r="G330">
+        <v>-0.6661795418934083</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331">
@@ -5995,6 +6987,9 @@
       <c r="F331">
         <v>0.1714587283557613</v>
       </c>
+      <c r="G331">
+        <v>0.1714587283557613</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332">
@@ -6012,6 +7007,9 @@
       <c r="F332">
         <v>0.124324905603994</v>
       </c>
+      <c r="G332">
+        <v>0.124324905603994</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333">
@@ -6029,6 +7027,9 @@
       <c r="F333">
         <v>0.1630342673633028</v>
       </c>
+      <c r="G333">
+        <v>0.1630342673633028</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334">
@@ -6046,6 +7047,9 @@
       <c r="F334">
         <v>-0.0009065692396882133</v>
       </c>
+      <c r="G334">
+        <v>-0.0009065692396882133</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335">
@@ -6063,6 +7067,9 @@
       <c r="F335">
         <v>-0.1067628596357108</v>
       </c>
+      <c r="G335">
+        <v>-0.1067628596357108</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336">
@@ -6080,6 +7087,9 @@
       <c r="F336">
         <v>0.048840433160727</v>
       </c>
+      <c r="G336">
+        <v>0.048840433160727</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337">
@@ -6097,6 +7107,9 @@
       <c r="F337">
         <v>-0.01190835742443304</v>
       </c>
+      <c r="G337">
+        <v>-0.01190835742443304</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338">
@@ -6114,6 +7127,9 @@
       <c r="F338">
         <v>-0.05833518632182169</v>
       </c>
+      <c r="G338">
+        <v>-0.05833518632182169</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339">
@@ -6131,6 +7147,9 @@
       <c r="F339">
         <v>-0.1850507074698486</v>
       </c>
+      <c r="G339">
+        <v>-0.1850507074698486</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340">
@@ -6148,6 +7167,9 @@
       <c r="F340">
         <v>-0.2594905747540274</v>
       </c>
+      <c r="G340">
+        <v>-0.2594905747540274</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341">
@@ -6165,6 +7187,9 @@
       <c r="F341">
         <v>-1.99917344337077</v>
       </c>
+      <c r="G341">
+        <v>-1.99917344337077</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342">
@@ -6182,6 +7207,9 @@
       <c r="F342">
         <v>-0.09937997597943873</v>
       </c>
+      <c r="G342">
+        <v>-0.09937997597943873</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343">
@@ -6199,6 +7227,9 @@
       <c r="F343">
         <v>-0.04959745924763728</v>
       </c>
+      <c r="G343">
+        <v>-0.04959745924763728</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344">
@@ -6216,6 +7247,9 @@
       <c r="F344">
         <v>-0.2006827115837605</v>
       </c>
+      <c r="G344">
+        <v>-0.2006827115837605</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345">
@@ -6233,6 +7267,9 @@
       <c r="F345">
         <v>-0.2662953711892758</v>
       </c>
+      <c r="G345">
+        <v>-0.2662953711892758</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346">
@@ -6250,6 +7287,9 @@
       <c r="F346">
         <v>-0.1439814458432114</v>
       </c>
+      <c r="G346">
+        <v>-0.1439814458432114</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347">
@@ -6267,6 +7307,9 @@
       <c r="F347">
         <v>1.810189147700705</v>
       </c>
+      <c r="G347">
+        <v>1.810189147700705</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348">
@@ -6284,6 +7327,9 @@
       <c r="F348">
         <v>-0.379060629204499</v>
       </c>
+      <c r="G348">
+        <v>-0.379060629204499</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349">
@@ -6301,6 +7347,9 @@
       <c r="F349">
         <v>1.207747073216867</v>
       </c>
+      <c r="G349">
+        <v>1.207747073216867</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350">
@@ -6318,6 +7367,9 @@
       <c r="F350">
         <v>-0.05651248439047608</v>
       </c>
+      <c r="G350">
+        <v>-0.05651248439047608</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351">
@@ -6335,6 +7387,9 @@
       <c r="F351">
         <v>-0.3678913697046837</v>
       </c>
+      <c r="G351">
+        <v>-0.3678913697046837</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352">
@@ -6352,6 +7407,9 @@
       <c r="F352">
         <v>-0.03355568245197441</v>
       </c>
+      <c r="G352">
+        <v>-0.03355568245197441</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353">
@@ -6369,6 +7427,9 @@
       <c r="F353">
         <v>-1.553813409719199</v>
       </c>
+      <c r="G353">
+        <v>-1.553813409719199</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354">
@@ -6386,6 +7447,9 @@
       <c r="F354">
         <v>-0.3069014405414353</v>
       </c>
+      <c r="G354">
+        <v>-0.3069014405414353</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355">
@@ -6403,6 +7467,9 @@
       <c r="F355">
         <v>-0.9806320290545721</v>
       </c>
+      <c r="G355">
+        <v>-0.9806320290545721</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356">
@@ -6420,6 +7487,9 @@
       <c r="F356">
         <v>0.4472641284529636</v>
       </c>
+      <c r="G356">
+        <v>0.4472641284529636</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357">
@@ -6437,6 +7507,9 @@
       <c r="F357">
         <v>-1.860511954577707</v>
       </c>
+      <c r="G357">
+        <v>-1.860511954577707</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358">
@@ -6454,6 +7527,9 @@
       <c r="F358">
         <v>1.582302623451168</v>
       </c>
+      <c r="G358">
+        <v>1.582302623451168</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359">
@@ -6471,6 +7547,9 @@
       <c r="F359">
         <v>-1.595495126542014</v>
       </c>
+      <c r="G359">
+        <v>-1.595495126542014</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360">
@@ -6488,6 +7567,9 @@
       <c r="F360">
         <v>0.8174845533376317</v>
       </c>
+      <c r="G360">
+        <v>0.8174845533376317</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361">
@@ -6505,6 +7587,9 @@
       <c r="F361">
         <v>0.1660822264838308</v>
       </c>
+      <c r="G361">
+        <v>0.1660822264838308</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362">
@@ -6522,6 +7607,9 @@
       <c r="F362">
         <v>0.2888066041268155</v>
       </c>
+      <c r="G362">
+        <v>0.2888066041268155</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363">
@@ -6539,6 +7627,9 @@
       <c r="F363">
         <v>0.3283133683624402</v>
       </c>
+      <c r="G363">
+        <v>0.3283133683624402</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364">
@@ -6556,6 +7647,9 @@
       <c r="F364">
         <v>0.1649555156111588</v>
       </c>
+      <c r="G364">
+        <v>0.1649555156111588</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365">
@@ -6573,6 +7667,9 @@
       <c r="F365">
         <v>0.03646545773854343</v>
       </c>
+      <c r="G365">
+        <v>0.03646545773854343</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366">
@@ -6590,6 +7687,9 @@
       <c r="F366">
         <v>0.2791231338438065</v>
       </c>
+      <c r="G366">
+        <v>0.2791231338438065</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367">
@@ -6607,6 +7707,9 @@
       <c r="F367">
         <v>0.8551996949039917</v>
       </c>
+      <c r="G367">
+        <v>0.8551996949039917</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368">
@@ -6624,6 +7727,9 @@
       <c r="F368">
         <v>1.020002510452545</v>
       </c>
+      <c r="G368">
+        <v>1.020002510452545</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369">
@@ -6641,6 +7747,9 @@
       <c r="F369">
         <v>0.9634188678888056</v>
       </c>
+      <c r="G369">
+        <v>0.9634188678888056</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370">
@@ -6658,6 +7767,9 @@
       <c r="F370">
         <v>0.912094866693855</v>
       </c>
+      <c r="G370">
+        <v>0.912094866693855</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371">
@@ -6675,6 +7787,9 @@
       <c r="F371">
         <v>-0.1010867464747772</v>
       </c>
+      <c r="G371">
+        <v>-0.1010867464747772</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372">
@@ -6692,6 +7807,9 @@
       <c r="F372">
         <v>-0.7225312592089121</v>
       </c>
+      <c r="G372">
+        <v>-0.7225312592089121</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373">
@@ -6709,6 +7827,9 @@
       <c r="F373">
         <v>-0.4674448021141586</v>
       </c>
+      <c r="G373">
+        <v>-0.4674448021141586</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374">
@@ -6726,6 +7847,9 @@
       <c r="F374">
         <v>-0.5153810184343569</v>
       </c>
+      <c r="G374">
+        <v>-0.5153810184343569</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375">
@@ -6743,6 +7867,9 @@
       <c r="F375">
         <v>-0.4809041447772106</v>
       </c>
+      <c r="G375">
+        <v>-0.4809041447772106</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376">
@@ -6760,6 +7887,9 @@
       <c r="F376">
         <v>0.2739286577168869</v>
       </c>
+      <c r="G376">
+        <v>0.2739286577168869</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377">
@@ -6777,6 +7907,9 @@
       <c r="F377">
         <v>0.2296515755318456</v>
       </c>
+      <c r="G377">
+        <v>0.2296515755318456</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378">
@@ -6794,6 +7927,9 @@
       <c r="F378">
         <v>0.416429595068508</v>
       </c>
+      <c r="G378">
+        <v>0.416429595068508</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379">
@@ -6811,6 +7947,9 @@
       <c r="F379">
         <v>0.2275599610761463</v>
       </c>
+      <c r="G379">
+        <v>0.2275599610761463</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380">
@@ -6828,6 +7967,9 @@
       <c r="F380">
         <v>0.09846626831015365</v>
       </c>
+      <c r="G380">
+        <v>0.09846626831015365</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381">
@@ -6845,6 +7987,9 @@
       <c r="F381">
         <v>0.1688438593177409</v>
       </c>
+      <c r="G381">
+        <v>0.1688438593177409</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382">
@@ -6862,6 +8007,9 @@
       <c r="F382">
         <v>0.3134982881829168</v>
       </c>
+      <c r="G382">
+        <v>0.3134982881829168</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383">
@@ -6879,6 +8027,9 @@
       <c r="F383">
         <v>0.353822080371305</v>
       </c>
+      <c r="G383">
+        <v>0.353822080371305</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384">
@@ -6896,6 +8047,9 @@
       <c r="F384">
         <v>0.1914457659654698</v>
       </c>
+      <c r="G384">
+        <v>0.1914457659654698</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385">
@@ -6913,6 +8067,9 @@
       <c r="F385">
         <v>0.0603273671021787</v>
       </c>
+      <c r="G385">
+        <v>0.0603273671021787</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386">
@@ -6930,6 +8087,9 @@
       <c r="F386">
         <v>0.5006882836398732</v>
       </c>
+      <c r="G386">
+        <v>0.5006882836398732</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387">
@@ -6947,6 +8107,9 @@
       <c r="F387">
         <v>-0.5956772190331979</v>
       </c>
+      <c r="G387">
+        <v>-0.5956772190331979</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388">
@@ -6964,6 +8127,9 @@
       <c r="F388">
         <v>-0.4739431844355708</v>
       </c>
+      <c r="G388">
+        <v>-0.4739431844355708</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389">
@@ -6981,6 +8147,9 @@
       <c r="F389">
         <v>-0.5595330769707776</v>
       </c>
+      <c r="G389">
+        <v>-0.5595330769707776</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390">
@@ -6998,6 +8167,9 @@
       <c r="F390">
         <v>-0.5221074551681486</v>
       </c>
+      <c r="G390">
+        <v>-0.5221074551681486</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391">
@@ -7015,6 +8187,9 @@
       <c r="F391">
         <v>-0.06211957888780759</v>
       </c>
+      <c r="G391">
+        <v>-0.06211957888780759</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392">
@@ -7032,6 +8207,9 @@
       <c r="F392">
         <v>-0.7182099472196752</v>
       </c>
+      <c r="G392">
+        <v>-0.7182099472196752</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393">
@@ -7049,6 +8227,9 @@
       <c r="F393">
         <v>-0.5864199066518888</v>
       </c>
+      <c r="G393">
+        <v>-0.5864199066518888</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394">
@@ -7066,6 +8247,9 @@
       <c r="F394">
         <v>-0.6450639561582405</v>
       </c>
+      <c r="G394">
+        <v>-0.6450639561582405</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395">
@@ -7083,6 +8267,9 @@
       <c r="F395">
         <v>-0.5781166848456886</v>
       </c>
+      <c r="G395">
+        <v>-0.5781166848456886</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396">
@@ -7100,6 +8287,9 @@
       <c r="F396">
         <v>0.2650200671181506</v>
       </c>
+      <c r="G396">
+        <v>0.2650200671181506</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397">
@@ -7117,6 +8307,9 @@
       <c r="F397">
         <v>1.435453081282793</v>
       </c>
+      <c r="G397">
+        <v>1.435453081282793</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398">
@@ -7134,6 +8327,9 @@
       <c r="F398">
         <v>-2.624949857128739</v>
       </c>
+      <c r="G398">
+        <v>-2.624949857128739</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399">
@@ -7151,6 +8347,9 @@
       <c r="F399">
         <v>-0.2187679044223879</v>
       </c>
+      <c r="G399">
+        <v>-0.2187679044223879</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400">
@@ -7168,6 +8367,9 @@
       <c r="F400">
         <v>0.5723012735242043</v>
       </c>
+      <c r="G400">
+        <v>0.5723012735242043</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401">
@@ -7185,6 +8387,9 @@
       <c r="F401">
         <v>-0.3539792319208523</v>
       </c>
+      <c r="G401">
+        <v>-0.3539792319208523</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402">
@@ -7202,6 +8407,9 @@
       <c r="F402">
         <v>1.137104191857083</v>
       </c>
+      <c r="G402">
+        <v>1.137104191857083</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403">
@@ -7219,6 +8427,9 @@
       <c r="F403">
         <v>-1.111560656239686</v>
       </c>
+      <c r="G403">
+        <v>-1.111560656239686</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404">
@@ -7236,6 +8447,9 @@
       <c r="F404">
         <v>0.317899735018111</v>
       </c>
+      <c r="G404">
+        <v>0.317899735018111</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405">
@@ -7253,6 +8467,9 @@
       <c r="F405">
         <v>-0.6334550827948842</v>
       </c>
+      <c r="G405">
+        <v>-0.6334550827948842</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406">
@@ -7270,6 +8487,9 @@
       <c r="F406">
         <v>0.0306182617617665</v>
       </c>
+      <c r="G406">
+        <v>0.0306182617617665</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407">
@@ -7287,6 +8507,9 @@
       <c r="F407">
         <v>-0.0930441417127853</v>
       </c>
+      <c r="G407">
+        <v>-0.0930441417127853</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408">
@@ -7304,6 +8527,9 @@
       <c r="F408">
         <v>-0.1001957627774754</v>
       </c>
+      <c r="G408">
+        <v>-0.1001957627774754</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409">
@@ -7321,6 +8547,9 @@
       <c r="F409">
         <v>-0.2371018766835581</v>
       </c>
+      <c r="G409">
+        <v>-0.2371018766835581</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410">
@@ -7338,6 +8567,9 @@
       <c r="F410">
         <v>-0.2951888637098488</v>
       </c>
+      <c r="G410">
+        <v>-0.2951888637098488</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411">
@@ -7355,6 +8587,9 @@
       <c r="F411">
         <v>0.1850057583160402</v>
       </c>
+      <c r="G411">
+        <v>0.1850057583160402</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412">
@@ -7372,6 +8607,9 @@
       <c r="F412">
         <v>0.4779866196284406</v>
       </c>
+      <c r="G412">
+        <v>0.4779866196284406</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413">
@@ -7389,6 +8627,9 @@
       <c r="F413">
         <v>0.5345830225202843</v>
       </c>
+      <c r="G413">
+        <v>0.5345830225202843</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414">
@@ -7406,6 +8647,9 @@
       <c r="F414">
         <v>0.3868584139906868</v>
       </c>
+      <c r="G414">
+        <v>0.3868584139906868</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415">
@@ -7423,6 +8667,9 @@
       <c r="F415">
         <v>0.2455303340017069</v>
       </c>
+      <c r="G415">
+        <v>0.2455303340017069</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416">
@@ -7440,6 +8687,9 @@
       <c r="F416">
         <v>-0.1434578660621654</v>
       </c>
+      <c r="G416">
+        <v>-0.1434578660621654</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417">
@@ -7457,6 +8707,9 @@
       <c r="F417">
         <v>-0.08762874387045329</v>
       </c>
+      <c r="G417">
+        <v>-0.08762874387045329</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418">
@@ -7474,6 +8727,9 @@
       <c r="F418">
         <v>-0.2536760500572433</v>
       </c>
+      <c r="G418">
+        <v>-0.2536760500572433</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419">
@@ -7491,6 +8747,9 @@
       <c r="F419">
         <v>-0.2481363978837038</v>
       </c>
+      <c r="G419">
+        <v>-0.2481363978837038</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420">
@@ -7508,6 +8767,9 @@
       <c r="F420">
         <v>-0.3714866251675719</v>
       </c>
+      <c r="G420">
+        <v>-0.3714866251675719</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421">
@@ -7525,6 +8787,9 @@
       <c r="F421">
         <v>-0.2900723715674419</v>
       </c>
+      <c r="G421">
+        <v>-0.2900723715674419</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422">
@@ -7542,6 +8807,9 @@
       <c r="F422">
         <v>0.2955115183361229</v>
       </c>
+      <c r="G422">
+        <v>0.2955115183361229</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423">
@@ -7559,6 +8827,9 @@
       <c r="F423">
         <v>-1.101122370722173</v>
       </c>
+      <c r="G423">
+        <v>-1.101122370722173</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424">
@@ -7576,6 +8847,9 @@
       <c r="F424">
         <v>-0.2058767139220488</v>
       </c>
+      <c r="G424">
+        <v>-0.2058767139220488</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425">
@@ -7593,6 +8867,9 @@
       <c r="F425">
         <v>-0.7160410096384652</v>
       </c>
+      <c r="G425">
+        <v>-0.7160410096384652</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426">
@@ -7610,6 +8887,9 @@
       <c r="F426">
         <v>-0.2085206569305557</v>
       </c>
+      <c r="G426">
+        <v>-0.2085206569305557</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427">
@@ -7627,6 +8907,9 @@
       <c r="F427">
         <v>-1.148365822531993</v>
       </c>
+      <c r="G427">
+        <v>-1.148365822531993</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428">
@@ -7644,6 +8927,9 @@
       <c r="F428">
         <v>-0.8107962323615285</v>
       </c>
+      <c r="G428">
+        <v>-0.8107962323615285</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429">
@@ -7661,6 +8947,9 @@
       <c r="F429">
         <v>-0.7904092220256194</v>
       </c>
+      <c r="G429">
+        <v>-0.7904092220256194</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430">
@@ -7678,6 +8967,9 @@
       <c r="F430">
         <v>-0.6642118395166825</v>
       </c>
+      <c r="G430">
+        <v>-0.6642118395166825</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431">
@@ -7695,6 +8987,9 @@
       <c r="F431">
         <v>-0.2088120128328644</v>
       </c>
+      <c r="G431">
+        <v>-0.2088120128328644</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432">
@@ -7712,6 +9007,9 @@
       <c r="F432">
         <v>-0.9543691492734185</v>
       </c>
+      <c r="G432">
+        <v>-0.9543691492734185</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433">
@@ -7729,6 +9027,9 @@
       <c r="F433">
         <v>-0.4933842956283268</v>
       </c>
+      <c r="G433">
+        <v>-0.4933842956283268</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434">
@@ -7746,6 +9047,9 @@
       <c r="F434">
         <v>-0.4358971633577167</v>
       </c>
+      <c r="G434">
+        <v>-0.4358971633577167</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435">
@@ -7763,6 +9067,9 @@
       <c r="F435">
         <v>-0.3735476885425929</v>
       </c>
+      <c r="G435">
+        <v>-0.3735476885425929</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436">
@@ -7780,6 +9087,9 @@
       <c r="F436">
         <v>0.06236970148922982</v>
       </c>
+      <c r="G436">
+        <v>0.06236970148922982</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437">
@@ -7797,6 +9107,9 @@
       <c r="F437">
         <v>-0.5365896650352305</v>
       </c>
+      <c r="G437">
+        <v>-0.5365896650352305</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438">
@@ -7814,6 +9127,9 @@
       <c r="F438">
         <v>-0.3593007599664256</v>
       </c>
+      <c r="G438">
+        <v>-0.3593007599664256</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439">
@@ -7831,6 +9147,9 @@
       <c r="F439">
         <v>-0.4854427852803214</v>
       </c>
+      <c r="G439">
+        <v>-0.4854427852803214</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440">
@@ -7848,6 +9167,9 @@
       <c r="F440">
         <v>-0.4681913994439221</v>
       </c>
+      <c r="G440">
+        <v>-0.4681913994439221</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441">
@@ -7865,6 +9187,9 @@
       <c r="F441">
         <v>-0.6517637914609811</v>
       </c>
+      <c r="G441">
+        <v>-0.6517637914609811</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442">
@@ -7882,6 +9207,9 @@
       <c r="F442">
         <v>1.732908708497801</v>
       </c>
+      <c r="G442">
+        <v>1.732908708497801</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443">
@@ -7899,6 +9227,9 @@
       <c r="F443">
         <v>-2.235620028475975</v>
       </c>
+      <c r="G443">
+        <v>-2.235620028475975</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444">
@@ -7916,6 +9247,9 @@
       <c r="F444">
         <v>0.7244587836954226</v>
       </c>
+      <c r="G444">
+        <v>0.7244587836954226</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445">
@@ -7933,6 +9267,9 @@
       <c r="F445">
         <v>-1.187483657981038</v>
       </c>
+      <c r="G445">
+        <v>-1.187483657981038</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446">
@@ -7950,6 +9287,9 @@
       <c r="F446">
         <v>0.5024881000529965</v>
       </c>
+      <c r="G446">
+        <v>0.5024881000529965</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447">
@@ -7967,6 +9307,9 @@
       <c r="F447">
         <v>-1.27470473098413</v>
       </c>
+      <c r="G447">
+        <v>-1.27470473098413</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448">
@@ -7984,6 +9327,9 @@
       <c r="F448">
         <v>0.0370955995035606</v>
       </c>
+      <c r="G448">
+        <v>0.0370955995035606</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449">
@@ -8001,6 +9347,9 @@
       <c r="F449">
         <v>-0.7161729811258166</v>
       </c>
+      <c r="G449">
+        <v>-0.7161729811258166</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450">
@@ -8018,6 +9367,9 @@
       <c r="F450">
         <v>-0.3603986779520013</v>
       </c>
+      <c r="G450">
+        <v>-0.3603986779520013</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451">
@@ -8035,6 +9387,9 @@
       <c r="F451">
         <v>1.031674952596387</v>
       </c>
+      <c r="G451">
+        <v>1.031674952596387</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452">
@@ -8052,6 +9407,9 @@
       <c r="F452">
         <v>1.388143713725611</v>
       </c>
+      <c r="G452">
+        <v>1.388143713725611</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453">
@@ -8069,6 +9427,9 @@
       <c r="F453">
         <v>1.571543509815605</v>
       </c>
+      <c r="G453">
+        <v>1.571543509815605</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454">
@@ -8086,6 +9447,9 @@
       <c r="F454">
         <v>1.767181874059021</v>
       </c>
+      <c r="G454">
+        <v>1.767181874059021</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455">
@@ -8103,6 +9467,9 @@
       <c r="F455">
         <v>2.239081638195351</v>
       </c>
+      <c r="G455">
+        <v>2.239081638195351</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456">
@@ -8120,6 +9487,9 @@
       <c r="F456">
         <v>-0.06812829834276334</v>
       </c>
+      <c r="G456">
+        <v>-0.06812829834276334</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457">
@@ -8137,6 +9507,9 @@
       <c r="F457">
         <v>-0.7241778456570415</v>
       </c>
+      <c r="G457">
+        <v>-0.7241778456570415</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458">
@@ -8154,6 +9527,9 @@
       <c r="F458">
         <v>-0.5897313878764803</v>
       </c>
+      <c r="G458">
+        <v>-0.5897313878764803</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459">
@@ -8171,6 +9547,9 @@
       <c r="F459">
         <v>-0.6479375810652473</v>
       </c>
+      <c r="G459">
+        <v>-0.6479375810652473</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460">
@@ -8188,6 +9567,9 @@
       <c r="F460">
         <v>-0.5799205290004803</v>
       </c>
+      <c r="G460">
+        <v>-0.5799205290004803</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461">
@@ -8205,6 +9587,9 @@
       <c r="F461">
         <v>0.3793765881160979</v>
       </c>
+      <c r="G461">
+        <v>0.3793765881160979</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462">
@@ -8222,6 +9607,9 @@
       <c r="F462">
         <v>1.702596207751754</v>
       </c>
+      <c r="G462">
+        <v>1.702596207751754</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463">
@@ -8239,6 +9627,9 @@
       <c r="F463">
         <v>2.198111621563247</v>
       </c>
+      <c r="G463">
+        <v>2.198111621563247</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464">
@@ -8256,6 +9647,9 @@
       <c r="F464">
         <v>3.07969596592318</v>
       </c>
+      <c r="G464">
+        <v>3.07969596592318</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465">
@@ -8273,6 +9667,9 @@
       <c r="F465">
         <v>3.092988736506623</v>
       </c>
+      <c r="G465">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466">
@@ -8290,6 +9687,9 @@
       <c r="F466">
         <v>0.06522247138550794</v>
       </c>
+      <c r="G466">
+        <v>0.06522247138550794</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467">
@@ -8307,6 +9707,9 @@
       <c r="F467">
         <v>-0.444449162552398</v>
       </c>
+      <c r="G467">
+        <v>-0.444449162552398</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468">
@@ -8324,6 +9727,9 @@
       <c r="F468">
         <v>-0.3091118214069479</v>
       </c>
+      <c r="G468">
+        <v>-0.3091118214069479</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469">
@@ -8341,6 +9747,9 @@
       <c r="F469">
         <v>-0.4359561545556863</v>
       </c>
+      <c r="G469">
+        <v>-0.4359561545556863</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470">
@@ -8358,6 +9767,9 @@
       <c r="F470">
         <v>-0.4361040310492736</v>
       </c>
+      <c r="G470">
+        <v>-0.4361040310492736</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471">
@@ -8375,6 +9787,9 @@
       <c r="F471">
         <v>0.1178146170769669</v>
       </c>
+      <c r="G471">
+        <v>0.1178146170769669</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472">
@@ -8392,6 +9807,9 @@
       <c r="F472">
         <v>-0.06251517999872458</v>
       </c>
+      <c r="G472">
+        <v>-0.06251517999872458</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473">
@@ -8409,6 +9827,9 @@
       <c r="F473">
         <v>-0.05572691634318517</v>
       </c>
+      <c r="G473">
+        <v>-0.05572691634318517</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474">
@@ -8426,6 +9847,9 @@
       <c r="F474">
         <v>-0.2267187870732138</v>
       </c>
+      <c r="G474">
+        <v>-0.2267187870732138</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475">
@@ -8443,6 +9867,9 @@
       <c r="F475">
         <v>-0.2948930873805551</v>
       </c>
+      <c r="G475">
+        <v>-0.2948930873805551</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476">
@@ -8460,6 +9887,9 @@
       <c r="F476">
         <v>0.1317642980526291</v>
       </c>
+      <c r="G476">
+        <v>0.1317642980526291</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477">
@@ -8477,6 +9907,9 @@
       <c r="F477">
         <v>0.08879647924531578</v>
       </c>
+      <c r="G477">
+        <v>0.08879647924531578</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478">
@@ -8494,6 +9927,9 @@
       <c r="F478">
         <v>0.1294946703518867</v>
       </c>
+      <c r="G478">
+        <v>0.1294946703518867</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479">
@@ -8511,6 +9947,9 @@
       <c r="F479">
         <v>-0.03390645578623231</v>
       </c>
+      <c r="G479">
+        <v>-0.03390645578623231</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480">
@@ -8528,6 +9967,9 @@
       <c r="F480">
         <v>-0.1338974513588831</v>
       </c>
+      <c r="G480">
+        <v>-0.1338974513588831</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481">
@@ -8545,6 +9987,9 @@
       <c r="F481">
         <v>0.1118661410720406</v>
       </c>
+      <c r="G481">
+        <v>0.1118661410720406</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482">
@@ -8562,6 +10007,9 @@
       <c r="F482">
         <v>0.04749277466884832</v>
       </c>
+      <c r="G482">
+        <v>0.04749277466884832</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483">
@@ -8579,6 +10027,9 @@
       <c r="F483">
         <v>0.104720557538466</v>
       </c>
+      <c r="G483">
+        <v>0.104720557538466</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484">
@@ -8596,6 +10047,9 @@
       <c r="F484">
         <v>-0.05315506099246872</v>
       </c>
+      <c r="G484">
+        <v>-0.05315506099246872</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485">
@@ -8613,6 +10067,9 @@
       <c r="F485">
         <v>-0.1489561857952294</v>
       </c>
+      <c r="G485">
+        <v>-0.1489561857952294</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486">
@@ -8630,6 +10087,9 @@
       <c r="F486">
         <v>0.1186238891068591</v>
       </c>
+      <c r="G486">
+        <v>0.1186238891068591</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487">
@@ -8647,6 +10107,9 @@
       <c r="F487">
         <v>-0.1178386715724887</v>
       </c>
+      <c r="G487">
+        <v>-0.1178386715724887</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488">
@@ -8664,6 +10127,9 @@
       <c r="F488">
         <v>-0.05502878309512699</v>
       </c>
+      <c r="G488">
+        <v>-0.05502878309512699</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489">
@@ -8681,6 +10147,9 @@
       <c r="F489">
         <v>-0.2065484937230209</v>
       </c>
+      <c r="G489">
+        <v>-0.2065484937230209</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490">
@@ -8698,6 +10167,9 @@
       <c r="F490">
         <v>-0.2707148655422537</v>
       </c>
+      <c r="G490">
+        <v>-0.2707148655422537</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491">
@@ -8715,6 +10187,9 @@
       <c r="F491">
         <v>0.09407500282094892</v>
       </c>
+      <c r="G491">
+        <v>0.09407500282094892</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492">
@@ -8732,6 +10207,9 @@
       <c r="F492">
         <v>-0.06882067906919279</v>
       </c>
+      <c r="G492">
+        <v>-0.06882067906919279</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493">
@@ -8749,6 +10227,9 @@
       <c r="F493">
         <v>-0.01929367714782598</v>
       </c>
+      <c r="G493">
+        <v>-0.01929367714782598</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494">
@@ -8766,6 +10247,9 @@
       <c r="F494">
         <v>-0.1730040580045183</v>
       </c>
+      <c r="G494">
+        <v>-0.1730040580045183</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495">
@@ -8783,6 +10267,9 @@
       <c r="F495">
         <v>-0.2449772997179978</v>
       </c>
+      <c r="G495">
+        <v>-0.2449772997179978</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496">
@@ -8800,6 +10287,9 @@
       <c r="F496">
         <v>0.2168723677180736</v>
       </c>
+      <c r="G496">
+        <v>0.2168723677180736</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497">
@@ -8817,6 +10307,9 @@
       <c r="F497">
         <v>0.5690442281227639</v>
       </c>
+      <c r="G497">
+        <v>0.5690442281227639</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498">
@@ -8834,6 +10327,9 @@
       <c r="F498">
         <v>0.6268469918458608</v>
       </c>
+      <c r="G498">
+        <v>0.6268469918458608</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499">
@@ -8851,6 +10347,9 @@
       <c r="F499">
         <v>0.4908867740822513</v>
       </c>
+      <c r="G499">
+        <v>0.4908867740822513</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500">
@@ -8868,6 +10367,9 @@
       <c r="F500">
         <v>0.3511482430913624</v>
       </c>
+      <c r="G500">
+        <v>0.3511482430913624</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501">
@@ -8885,6 +10387,9 @@
       <c r="F501">
         <v>0.01874073377945644</v>
       </c>
+      <c r="G501">
+        <v>0.01874073377945644</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502">
@@ -8902,6 +10407,9 @@
       <c r="F502">
         <v>-0.5543235045889398</v>
       </c>
+      <c r="G502">
+        <v>-0.5543235045889398</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503">
@@ -8919,6 +10427,9 @@
       <c r="F503">
         <v>-0.4612312046689412</v>
       </c>
+      <c r="G503">
+        <v>-0.4612312046689412</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504">
@@ -8936,6 +10447,9 @@
       <c r="F504">
         <v>-0.5547880771510966</v>
       </c>
+      <c r="G504">
+        <v>-0.5547880771510966</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505">
@@ -8953,6 +10467,9 @@
       <c r="F505">
         <v>-0.5204290913802706</v>
       </c>
+      <c r="G505">
+        <v>-0.5204290913802706</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506">
@@ -8970,6 +10487,9 @@
       <c r="F506">
         <v>0.09136300620167116</v>
       </c>
+      <c r="G506">
+        <v>0.09136300620167116</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507">
@@ -8987,6 +10507,9 @@
       <c r="F507">
         <v>2.483731575195818</v>
       </c>
+      <c r="G507">
+        <v>2.483731575195818</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508">
@@ -9004,6 +10527,9 @@
       <c r="F508">
         <v>0.413858272202678</v>
       </c>
+      <c r="G508">
+        <v>0.413858272202678</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509">
@@ -9021,6 +10547,9 @@
       <c r="F509">
         <v>3.051803049732158</v>
       </c>
+      <c r="G509">
+        <v>3.051803049732158</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510">
@@ -9038,6 +10567,9 @@
       <c r="F510">
         <v>1.678524224609192</v>
       </c>
+      <c r="G510">
+        <v>1.678524224609192</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511">
@@ -9055,6 +10587,9 @@
       <c r="F511">
         <v>-0.005630788516883771</v>
       </c>
+      <c r="G511">
+        <v>-0.005630788516883771</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512">
@@ -9072,6 +10607,9 @@
       <c r="F512">
         <v>-0.5617071907887073</v>
       </c>
+      <c r="G512">
+        <v>-0.5617071907887073</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513">
@@ -9089,6 +10627,9 @@
       <c r="F513">
         <v>-0.4439163536626194</v>
       </c>
+      <c r="G513">
+        <v>-0.4439163536626194</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514">
@@ -9106,6 +10647,9 @@
       <c r="F514">
         <v>-0.5349650750946786</v>
       </c>
+      <c r="G514">
+        <v>-0.5349650750946786</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515">
@@ -9123,6 +10667,9 @@
       <c r="F515">
         <v>-0.5057245074478687</v>
       </c>
+      <c r="G515">
+        <v>-0.5057245074478687</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516">
@@ -9140,6 +10687,9 @@
       <c r="F516">
         <v>0.3571039886477888</v>
       </c>
+      <c r="G516">
+        <v>0.3571039886477888</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517">
@@ -9157,6 +10707,9 @@
       <c r="F517">
         <v>1.554638122521856</v>
       </c>
+      <c r="G517">
+        <v>1.554638122521856</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518">
@@ -9174,6 +10727,9 @@
       <c r="F518">
         <v>1.938581430080113</v>
       </c>
+      <c r="G518">
+        <v>1.938581430080113</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519">
@@ -9191,6 +10747,9 @@
       <c r="F519">
         <v>2.513798296039485</v>
       </c>
+      <c r="G519">
+        <v>2.513798296039485</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520">
@@ -9208,6 +10767,9 @@
       <c r="F520">
         <v>3.092988736506623</v>
       </c>
+      <c r="G520">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521">
@@ -9225,6 +10787,9 @@
       <c r="F521">
         <v>0.2431529986302991</v>
       </c>
+      <c r="G521">
+        <v>0.2431529986302991</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522">
@@ -9242,6 +10807,9 @@
       <c r="F522">
         <v>0.3786941061465783</v>
       </c>
+      <c r="G522">
+        <v>0.3786941061465783</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523">
@@ -9259,6 +10827,9 @@
       <c r="F523">
         <v>0.5110091768082816</v>
       </c>
+      <c r="G523">
+        <v>0.5110091768082816</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524">
@@ -9276,6 +10847,9 @@
       <c r="F524">
         <v>0.3398689111964477</v>
       </c>
+      <c r="G524">
+        <v>0.3398689111964477</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525">
@@ -9293,6 +10867,9 @@
       <c r="F525">
         <v>0.203466154521287</v>
       </c>
+      <c r="G525">
+        <v>0.203466154521287</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526">
@@ -9310,6 +10887,9 @@
       <c r="F526">
         <v>0.3941630789020917</v>
       </c>
+      <c r="G526">
+        <v>0.3941630789020917</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527">
@@ -9327,6 +10907,9 @@
       <c r="F527">
         <v>1.663979948551616</v>
       </c>
+      <c r="G527">
+        <v>1.663979948551616</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528">
@@ -9344,6 +10927,9 @@
       <c r="F528">
         <v>1.87616910357638</v>
       </c>
+      <c r="G528">
+        <v>1.87616910357638</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529">
@@ -9361,6 +10947,9 @@
       <c r="F529">
         <v>2.124483820830743</v>
       </c>
+      <c r="G529">
+        <v>2.124483820830743</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530">
@@ -9378,6 +10967,9 @@
       <c r="F530">
         <v>2.833935740120292</v>
       </c>
+      <c r="G530">
+        <v>2.833935740120292</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531">
@@ -9395,6 +10987,9 @@
       <c r="F531">
         <v>-0.4727338928944561</v>
       </c>
+      <c r="G531">
+        <v>-0.4727338928944561</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532">
@@ -9412,6 +11007,9 @@
       <c r="F532">
         <v>0.1689775952338561</v>
       </c>
+      <c r="G532">
+        <v>0.1689775952338561</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533">
@@ -9429,6 +11027,9 @@
       <c r="F533">
         <v>-1.004716562299804</v>
       </c>
+      <c r="G533">
+        <v>-1.004716562299804</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534">
@@ -9446,6 +11047,9 @@
       <c r="F534">
         <v>-0.4569465735280592</v>
       </c>
+      <c r="G534">
+        <v>-0.4569465735280592</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535">
@@ -9463,6 +11067,9 @@
       <c r="F535">
         <v>-0.6358101457913586</v>
       </c>
+      <c r="G535">
+        <v>-0.6358101457913586</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536">
@@ -9480,6 +11087,9 @@
       <c r="F536">
         <v>0.0387937350262078</v>
       </c>
+      <c r="G536">
+        <v>0.0387937350262078</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537">
@@ -9497,6 +11107,9 @@
       <c r="F537">
         <v>-0.4003708433544443</v>
       </c>
+      <c r="G537">
+        <v>-0.4003708433544443</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538">
@@ -9514,6 +11127,9 @@
       <c r="F538">
         <v>-0.3154230710204038</v>
       </c>
+      <c r="G538">
+        <v>-0.3154230710204038</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539">
@@ -9531,6 +11147,9 @@
       <c r="F539">
         <v>-0.4310720642278292</v>
       </c>
+      <c r="G539">
+        <v>-0.4310720642278292</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540">
@@ -9548,6 +11167,9 @@
       <c r="F540">
         <v>-0.4347106981384413</v>
       </c>
+      <c r="G540">
+        <v>-0.4347106981384413</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541">
@@ -9565,6 +11187,9 @@
       <c r="F541">
         <v>0.1764684281259182</v>
       </c>
+      <c r="G541">
+        <v>0.1764684281259182</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542">
@@ -9582,6 +11207,9 @@
       <c r="F542">
         <v>0.2045108882892501</v>
       </c>
+      <c r="G542">
+        <v>0.2045108882892501</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543">
@@ -9599,6 +11227,9 @@
       <c r="F543">
         <v>0.2199626882354722</v>
       </c>
+      <c r="G543">
+        <v>0.2199626882354722</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544">
@@ -9616,6 +11247,9 @@
       <c r="F544">
         <v>0.05167401015788861</v>
       </c>
+      <c r="G544">
+        <v>0.05167401015788861</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545">
@@ -9633,6 +11267,9 @@
       <c r="F545">
         <v>-0.0629215242549394</v>
       </c>
+      <c r="G545">
+        <v>-0.0629215242549394</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546">
@@ -9650,6 +11287,9 @@
       <c r="F546">
         <v>0.003455654235970641</v>
       </c>
+      <c r="G546">
+        <v>0.003455654235970641</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547">
@@ -9667,6 +11307,9 @@
       <c r="F547">
         <v>-0.4554512072441623</v>
       </c>
+      <c r="G547">
+        <v>-0.4554512072441623</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548">
@@ -9684,6 +11327,9 @@
       <c r="F548">
         <v>-0.3774037678922661</v>
       </c>
+      <c r="G548">
+        <v>-0.3774037678922661</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549">
@@ -9701,6 +11347,9 @@
       <c r="F549">
         <v>-0.4796732709945183</v>
       </c>
+      <c r="G549">
+        <v>-0.4796732709945183</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550">
@@ -9718,6 +11367,9 @@
       <c r="F550">
         <v>-0.4685728744952475</v>
       </c>
+      <c r="G550">
+        <v>-0.4685728744952475</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551">
@@ -9735,6 +11387,9 @@
       <c r="F551">
         <v>0.0907853310145752</v>
       </c>
+      <c r="G551">
+        <v>0.0907853310145752</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552">
@@ -9752,6 +11407,9 @@
       <c r="F552">
         <v>0.2517573234139994</v>
       </c>
+      <c r="G552">
+        <v>0.2517573234139994</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553">
@@ -9769,6 +11427,9 @@
       <c r="F553">
         <v>0.1891449500524656</v>
       </c>
+      <c r="G553">
+        <v>0.1891449500524656</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554">
@@ -9786,6 +11447,9 @@
       <c r="F554">
         <v>0.05064992421464884</v>
       </c>
+      <c r="G554">
+        <v>0.05064992421464884</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555">
@@ -9803,6 +11467,9 @@
       <c r="F555">
         <v>-0.06905919719001689</v>
       </c>
+      <c r="G555">
+        <v>-0.06905919719001689</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556">
@@ -9820,6 +11487,9 @@
       <c r="F556">
         <v>0.09930758795407782</v>
       </c>
+      <c r="G556">
+        <v>0.09930758795407782</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557">
@@ -9837,6 +11507,9 @@
       <c r="F557">
         <v>-0.1004983506257323</v>
       </c>
+      <c r="G557">
+        <v>-0.1004983506257323</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558">
@@ -9854,6 +11527,9 @@
       <c r="F558">
         <v>-0.05142600916808263</v>
       </c>
+      <c r="G558">
+        <v>-0.05142600916808263</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559">
@@ -9871,6 +11547,9 @@
       <c r="F559">
         <v>-0.2023810269296589</v>
       </c>
+      <c r="G559">
+        <v>-0.2023810269296589</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560">
@@ -9888,6 +11567,9 @@
       <c r="F560">
         <v>-0.2675972217298235</v>
       </c>
+      <c r="G560">
+        <v>-0.2675972217298235</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561">
@@ -9905,6 +11587,9 @@
       <c r="F561">
         <v>0.2607802076720175</v>
       </c>
+      <c r="G561">
+        <v>0.2607802076720175</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562">
@@ -9922,6 +11607,9 @@
       <c r="F562">
         <v>0.7525178676547554</v>
       </c>
+      <c r="G562">
+        <v>0.7525178676547554</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563">
@@ -9939,6 +11627,9 @@
       <c r="F563">
         <v>0.8671840118899433</v>
       </c>
+      <c r="G563">
+        <v>0.8671840118899433</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564">
@@ -9956,6 +11647,9 @@
       <c r="F564">
         <v>0.7773421312318622</v>
       </c>
+      <c r="G564">
+        <v>0.7773421312318622</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565">
@@ -9973,6 +11667,9 @@
       <c r="F565">
         <v>0.672261487650135</v>
       </c>
+      <c r="G565">
+        <v>0.672261487650135</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566">
@@ -9990,6 +11687,9 @@
       <c r="F566">
         <v>-0.07496666262028795</v>
       </c>
+      <c r="G566">
+        <v>-0.07496666262028795</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567">
@@ -10007,6 +11707,9 @@
       <c r="F567">
         <v>-0.8765213533152364</v>
       </c>
+      <c r="G567">
+        <v>-0.8765213533152364</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568">
@@ -10024,6 +11727,9 @@
       <c r="F568">
         <v>-0.6780432330972771</v>
       </c>
+      <c r="G568">
+        <v>-0.6780432330972771</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569">
@@ -10041,6 +11747,9 @@
       <c r="F569">
         <v>-0.7095047361827759</v>
       </c>
+      <c r="G569">
+        <v>-0.7095047361827759</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570">
@@ -10058,6 +11767,9 @@
       <c r="F570">
         <v>-0.6172337293661768</v>
       </c>
+      <c r="G570">
+        <v>-0.6172337293661768</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571">
@@ -10075,6 +11787,9 @@
       <c r="F571">
         <v>0.6216917169431001</v>
       </c>
+      <c r="G571">
+        <v>0.6216917169431001</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572">
@@ -10092,6 +11807,9 @@
       <c r="F572">
         <v>3.89635068814966</v>
       </c>
+      <c r="G572">
+        <v>3.89635068814966</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573">
@@ -10109,6 +11827,9 @@
       <c r="F573">
         <v>-1.597084421344438</v>
       </c>
+      <c r="G573">
+        <v>-1.597084421344438</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574">
@@ -10126,6 +11847,9 @@
       <c r="F574">
         <v>-2.875349315640119</v>
       </c>
+      <c r="G574">
+        <v>-2.875349315640119</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575">
@@ -10143,6 +11867,9 @@
       <c r="F575">
         <v>1.230605526559453</v>
       </c>
+      <c r="G575">
+        <v>1.230605526559453</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576">
@@ -10160,6 +11887,9 @@
       <c r="F576">
         <v>0.04010684209783009</v>
       </c>
+      <c r="G576">
+        <v>0.04010684209783009</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577">
@@ -10177,6 +11907,9 @@
       <c r="F577">
         <v>-0.3788311609910465</v>
       </c>
+      <c r="G577">
+        <v>-0.3788311609910465</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578">
@@ -10194,6 +11927,9 @@
       <c r="F578">
         <v>-0.296595747925707</v>
       </c>
+      <c r="G578">
+        <v>-0.296595747925707</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579">
@@ -10211,6 +11947,9 @@
       <c r="F579">
         <v>-0.4153792098856444</v>
       </c>
+      <c r="G579">
+        <v>-0.4153792098856444</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580">
@@ -10228,6 +11967,9 @@
       <c r="F580">
         <v>-0.423722959004616</v>
       </c>
+      <c r="G580">
+        <v>-0.423722959004616</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581">
@@ -10245,6 +11987,9 @@
       <c r="F581">
         <v>-0.289598821876469</v>
       </c>
+      <c r="G581">
+        <v>-0.289598821876469</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582">
@@ -10262,6 +12007,9 @@
       <c r="F582">
         <v>-0.6396104857277036</v>
       </c>
+      <c r="G582">
+        <v>-0.6396104857277036</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583">
@@ -10279,6 +12027,9 @@
       <c r="F583">
         <v>-0.5399267804994501</v>
       </c>
+      <c r="G583">
+        <v>-0.5399267804994501</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584">
@@ -10296,6 +12047,9 @@
       <c r="F584">
         <v>-0.5985216372352813</v>
       </c>
+      <c r="G584">
+        <v>-0.5985216372352813</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585">
@@ -10313,6 +12067,9 @@
       <c r="F585">
         <v>-0.552173329418684</v>
       </c>
+      <c r="G585">
+        <v>-0.552173329418684</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586">
@@ -10330,6 +12087,9 @@
       <c r="F586">
         <v>0.1436988978626206</v>
       </c>
+      <c r="G586">
+        <v>0.1436988978626206</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587">
@@ -10347,6 +12107,9 @@
       <c r="F587">
         <v>-0.6491522079271955</v>
       </c>
+      <c r="G587">
+        <v>-0.6491522079271955</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588">
@@ -10364,6 +12127,9 @@
       <c r="F588">
         <v>-0.1405970277208918</v>
       </c>
+      <c r="G588">
+        <v>-0.1405970277208918</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589">
@@ -10381,6 +12147,9 @@
       <c r="F589">
         <v>-0.4662281299006569</v>
       </c>
+      <c r="G589">
+        <v>-0.4662281299006569</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590">
@@ -10398,6 +12167,9 @@
       <c r="F590">
         <v>-0.3860429896776552</v>
       </c>
+      <c r="G590">
+        <v>-0.3860429896776552</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591">
@@ -10415,6 +12187,9 @@
       <c r="F591">
         <v>0.04815219092540127</v>
       </c>
+      <c r="G591">
+        <v>0.04815219092540127</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592">
@@ -10432,6 +12207,9 @@
       <c r="F592">
         <v>-0.4018803832238379</v>
       </c>
+      <c r="G592">
+        <v>-0.4018803832238379</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593">
@@ -10449,6 +12227,9 @@
       <c r="F593">
         <v>-0.3140124569415016</v>
       </c>
+      <c r="G593">
+        <v>-0.3140124569415016</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594">
@@ -10466,6 +12247,9 @@
       <c r="F594">
         <v>-0.4299812385574642</v>
       </c>
+      <c r="G594">
+        <v>-0.4299812385574642</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595">
@@ -10483,6 +12267,9 @@
       <c r="F595">
         <v>-0.4339431839137399</v>
       </c>
+      <c r="G595">
+        <v>-0.4339431839137399</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596">
@@ -10500,6 +12287,9 @@
       <c r="F596">
         <v>0.1785370071400792</v>
       </c>
+      <c r="G596">
+        <v>0.1785370071400792</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597">
@@ -10517,6 +12307,9 @@
       <c r="F597">
         <v>-0.01454594725025309</v>
       </c>
+      <c r="G597">
+        <v>-0.01454594725025309</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598">
@@ -10534,6 +12327,9 @@
       <c r="F598">
         <v>0.1370878565849604</v>
       </c>
+      <c r="G598">
+        <v>0.1370878565849604</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599">
@@ -10551,6 +12347,9 @@
       <c r="F599">
         <v>-0.05688161853909271</v>
       </c>
+      <c r="G599">
+        <v>-0.05688161853909271</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600">
@@ -10568,6 +12367,9 @@
       <c r="F600">
         <v>-0.1454238329445506</v>
       </c>
+      <c r="G600">
+        <v>-0.1454238329445506</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601">
@@ -10585,6 +12387,9 @@
       <c r="F601">
         <v>0.1505661527387842</v>
       </c>
+      <c r="G601">
+        <v>0.1505661527387842</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602">
@@ -10602,6 +12407,9 @@
       <c r="F602">
         <v>-0.09168612504596595</v>
       </c>
+      <c r="G602">
+        <v>-0.09168612504596595</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603">
@@ -10619,6 +12427,9 @@
       <c r="F603">
         <v>-0.08362414343053984</v>
       </c>
+      <c r="G603">
+        <v>-0.08362414343053984</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604">
@@ -10636,6 +12447,9 @@
       <c r="F604">
         <v>-0.2369984753589974</v>
       </c>
+      <c r="G604">
+        <v>-0.2369984753589974</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605">
@@ -10653,6 +12467,9 @@
       <c r="F605">
         <v>-0.2945554702908571</v>
       </c>
+      <c r="G605">
+        <v>-0.2945554702908571</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606">
@@ -10670,6 +12487,9 @@
       <c r="F606">
         <v>0.3257061456512242</v>
       </c>
+      <c r="G606">
+        <v>0.3257061456512242</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607">
@@ -10687,6 +12507,9 @@
       <c r="F607">
         <v>0.9459788987811306</v>
       </c>
+      <c r="G607">
+        <v>0.9459788987811306</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608">
@@ -10704,6 +12527,9 @@
       <c r="F608">
         <v>1.272616566361166</v>
       </c>
+      <c r="G608">
+        <v>1.272616566361166</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609">
@@ -10721,6 +12547,9 @@
       <c r="F609">
         <v>1.243638563118837</v>
       </c>
+      <c r="G609">
+        <v>1.243638563118837</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610">
@@ -10738,6 +12567,9 @@
       <c r="F610">
         <v>1.35476141252941</v>
       </c>
+      <c r="G610">
+        <v>1.35476141252941</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611">
@@ -10755,6 +12587,9 @@
       <c r="F611">
         <v>0.04217030234967285</v>
       </c>
+      <c r="G611">
+        <v>0.04217030234967285</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612">
@@ -10772,6 +12607,9 @@
       <c r="F612">
         <v>-0.1576448522311814</v>
       </c>
+      <c r="G612">
+        <v>-0.1576448522311814</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613">
@@ -10789,6 +12627,9 @@
       <c r="F613">
         <v>-0.1443611603910261</v>
       </c>
+      <c r="G613">
+        <v>-0.1443611603910261</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614">
@@ -10806,6 +12647,9 @@
       <c r="F614">
         <v>-0.27755782818594</v>
       </c>
+      <c r="G614">
+        <v>-0.27755782818594</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615">
@@ -10823,6 +12667,9 @@
       <c r="F615">
         <v>-0.3254070239241524</v>
       </c>
+      <c r="G615">
+        <v>-0.3254070239241524</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616">
@@ -10840,6 +12687,9 @@
       <c r="F616">
         <v>0.1908049953781798</v>
       </c>
+      <c r="G616">
+        <v>0.1908049953781798</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617">
@@ -10857,6 +12707,9 @@
       <c r="F617">
         <v>0.3812019145343626</v>
       </c>
+      <c r="G617">
+        <v>0.3812019145343626</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618">
@@ -10874,6 +12727,9 @@
       <c r="F618">
         <v>0.4119785284783635</v>
       </c>
+      <c r="G618">
+        <v>0.4119785284783635</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619">
@@ -10891,6 +12747,9 @@
       <c r="F619">
         <v>0.249838197184943</v>
       </c>
+      <c r="G619">
+        <v>0.249838197184943</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620">
@@ -10908,6 +12767,9 @@
       <c r="F620">
         <v>0.1133683404247148</v>
       </c>
+      <c r="G620">
+        <v>0.1133683404247148</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621">
@@ -10925,6 +12787,9 @@
       <c r="F621">
         <v>0.2277275296221838</v>
       </c>
+      <c r="G621">
+        <v>0.2277275296221838</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622">
@@ -10942,6 +12807,9 @@
       <c r="F622">
         <v>0.9379152554125978</v>
       </c>
+      <c r="G622">
+        <v>0.9379152554125978</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623">
@@ -10959,6 +12827,9 @@
       <c r="F623">
         <v>1.106553305293509</v>
       </c>
+      <c r="G623">
+        <v>1.106553305293509</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624">
@@ -10976,6 +12847,9 @@
       <c r="F624">
         <v>1.106579855429725</v>
       </c>
+      <c r="G624">
+        <v>1.106579855429725</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625">
@@ -10993,6 +12867,9 @@
       <c r="F625">
         <v>1.104135581608383</v>
       </c>
+      <c r="G625">
+        <v>1.104135581608383</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626">
@@ -11010,6 +12887,9 @@
       <c r="F626">
         <v>-0.02277385417925815</v>
       </c>
+      <c r="G626">
+        <v>-0.02277385417925815</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627">
@@ -11027,6 +12907,9 @@
       <c r="F627">
         <v>-0.6515309117850149</v>
       </c>
+      <c r="G627">
+        <v>-0.6515309117850149</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628">
@@ -11044,6 +12927,9 @@
       <c r="F628">
         <v>-0.5192061489205566</v>
       </c>
+      <c r="G628">
+        <v>-0.5192061489205566</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629">
@@ -11061,6 +12947,9 @@
       <c r="F629">
         <v>-0.5945831587691099</v>
       </c>
+      <c r="G629">
+        <v>-0.5945831587691099</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630">
@@ -11078,6 +12967,9 @@
       <c r="F630">
         <v>-0.5452640250118326</v>
       </c>
+      <c r="G630">
+        <v>-0.5452640250118326</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631">
@@ -11095,6 +12987,9 @@
       <c r="F631">
         <v>-0.1899596644951345</v>
       </c>
+      <c r="G631">
+        <v>-0.1899596644951345</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632">
@@ -11112,6 +13007,9 @@
       <c r="F632">
         <v>1.312066067071586</v>
       </c>
+      <c r="G632">
+        <v>1.312066067071586</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633">
@@ -11129,6 +13027,9 @@
       <c r="F633">
         <v>-0.8893654338392429</v>
       </c>
+      <c r="G633">
+        <v>-0.8893654338392429</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634">
@@ -11146,6 +13047,9 @@
       <c r="F634">
         <v>0.6866352351306246</v>
       </c>
+      <c r="G634">
+        <v>0.6866352351306246</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635">
@@ -11163,6 +13067,9 @@
       <c r="F635">
         <v>-0.5892494518586822</v>
       </c>
+      <c r="G635">
+        <v>-0.5892494518586822</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636">
@@ -11180,6 +13087,9 @@
       <c r="F636">
         <v>0.1061990366761776</v>
       </c>
+      <c r="G636">
+        <v>0.1061990366761776</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637">
@@ -11197,6 +13107,9 @@
       <c r="F637">
         <v>0.3867802146455654</v>
       </c>
+      <c r="G637">
+        <v>0.3867802146455654</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638">
@@ -11214,6 +13127,9 @@
       <c r="F638">
         <v>0.6226444860542246</v>
       </c>
+      <c r="G638">
+        <v>0.6226444860542246</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639">
@@ -11231,6 +13147,9 @@
       <c r="F639">
         <v>0.573553643896055</v>
       </c>
+      <c r="G639">
+        <v>0.573553643896055</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640">
@@ -11248,6 +13167,9 @@
       <c r="F640">
         <v>0.4742564472841849</v>
       </c>
+      <c r="G640">
+        <v>0.4742564472841849</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641">
@@ -11265,6 +13187,9 @@
       <c r="F641">
         <v>0.1217468519564123</v>
       </c>
+      <c r="G641">
+        <v>0.1217468519564123</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642">
@@ -11282,6 +13207,9 @@
       <c r="F642">
         <v>-0.08422683424334571</v>
       </c>
+      <c r="G642">
+        <v>-0.08422683424334571</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643">
@@ -11299,6 +13227,9 @@
       <c r="F643">
         <v>-0.02617370361565235</v>
       </c>
+      <c r="G643">
+        <v>-0.02617370361565235</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644">
@@ -11316,6 +13247,9 @@
       <c r="F644">
         <v>-0.1801162063848037</v>
       </c>
+      <c r="G644">
+        <v>-0.1801162063848037</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645">
@@ -11333,6 +13267,9 @@
       <c r="F645">
         <v>-0.250433405042878</v>
       </c>
+      <c r="G645">
+        <v>-0.250433405042878</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646">
@@ -11350,6 +13287,9 @@
       <c r="F646">
         <v>0.3743568127956508</v>
       </c>
+      <c r="G646">
+        <v>0.3743568127956508</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647">
@@ -11367,6 +13307,9 @@
       <c r="F647">
         <v>1.216421797175963</v>
       </c>
+      <c r="G647">
+        <v>1.216421797175963</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648">
@@ -11384,6 +13327,9 @@
       <c r="F648">
         <v>1.166759787460251</v>
       </c>
+      <c r="G648">
+        <v>1.166759787460251</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649">
@@ -11401,6 +13347,9 @@
       <c r="F649">
         <v>1.042935391095013</v>
       </c>
+      <c r="G649">
+        <v>1.042935391095013</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650">
@@ -11418,6 +13367,9 @@
       <c r="F650">
         <v>0.9454881615987324</v>
       </c>
+      <c r="G650">
+        <v>0.9454881615987324</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651">
@@ -11435,6 +13387,9 @@
       <c r="F651">
         <v>0.07390489287095929</v>
       </c>
+      <c r="G651">
+        <v>0.07390489287095929</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652">
@@ -11452,6 +13407,9 @@
       <c r="F652">
         <v>-0.7220297738842032</v>
       </c>
+      <c r="G652">
+        <v>-0.7220297738842032</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653">
@@ -11469,6 +13427,9 @@
       <c r="F653">
         <v>-0.3995745286548104</v>
       </c>
+      <c r="G653">
+        <v>-0.3995745286548104</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654">
@@ -11486,6 +13447,9 @@
       <c r="F654">
         <v>-0.5622646161521093</v>
       </c>
+      <c r="G654">
+        <v>-0.5622646161521093</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655">
@@ -11503,6 +13467,9 @@
       <c r="F655">
         <v>-0.5056011173981974</v>
       </c>
+      <c r="G655">
+        <v>-0.5056011173981974</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656">
@@ -11520,6 +13487,9 @@
       <c r="F656">
         <v>0.1375374809572669</v>
       </c>
+      <c r="G656">
+        <v>0.1375374809572669</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657">
@@ -11537,6 +13507,9 @@
       <c r="F657">
         <v>0.1555347052834222</v>
       </c>
+      <c r="G657">
+        <v>0.1555347052834222</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658">
@@ -11554,6 +13527,9 @@
       <c r="F658">
         <v>0.1982619811758681</v>
       </c>
+      <c r="G658">
+        <v>0.1982619811758681</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659">
@@ -11571,6 +13547,9 @@
       <c r="F659">
         <v>0.03427804625015075</v>
       </c>
+      <c r="G659">
+        <v>0.03427804625015075</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660">
@@ -11588,6 +13567,9 @@
       <c r="F660">
         <v>-0.07716042925813504</v>
       </c>
+      <c r="G660">
+        <v>-0.07716042925813504</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661">
@@ -11605,6 +13587,9 @@
       <c r="F661">
         <v>0.09271706705982198</v>
       </c>
+      <c r="G661">
+        <v>0.09271706705982198</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662">
@@ -11622,6 +13607,9 @@
       <c r="F662">
         <v>-0.4118779342697408</v>
       </c>
+      <c r="G662">
+        <v>-0.4118779342697408</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663">
@@ -11639,6 +13627,9 @@
       <c r="F663">
         <v>-0.3826974966271819</v>
       </c>
+      <c r="G663">
+        <v>-0.3826974966271819</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664">
@@ -11656,6 +13647,9 @@
       <c r="F664">
         <v>-0.4974132347833455</v>
       </c>
+      <c r="G664">
+        <v>-0.4974132347833455</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665">
@@ -11673,6 +13667,9 @@
       <c r="F665">
         <v>-0.4822253487964743</v>
       </c>
+      <c r="G665">
+        <v>-0.4822253487964743</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666">
@@ -11690,6 +13687,9 @@
       <c r="F666">
         <v>0.1136201547639399</v>
       </c>
+      <c r="G666">
+        <v>0.1136201547639399</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667">
@@ -11707,6 +13707,9 @@
       <c r="F667">
         <v>-0.2821200088449199</v>
       </c>
+      <c r="G667">
+        <v>-0.2821200088449199</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668">
@@ -11724,6 +13727,9 @@
       <c r="F668">
         <v>-0.3281742009488091</v>
       </c>
+      <c r="G668">
+        <v>-0.3281742009488091</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669">
@@ -11741,6 +13747,9 @@
       <c r="F669">
         <v>-0.4878980042418285</v>
       </c>
+      <c r="G669">
+        <v>-0.4878980042418285</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670">
@@ -11758,6 +13767,9 @@
       <c r="F670">
         <v>-0.4895106451947592</v>
       </c>
+      <c r="G670">
+        <v>-0.4895106451947592</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671">
@@ -11775,6 +13787,9 @@
       <c r="F671">
         <v>-0.06901377167860716</v>
       </c>
+      <c r="G671">
+        <v>-0.06901377167860716</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672">
@@ -11792,6 +13807,9 @@
       <c r="F672">
         <v>0.7399446798767907</v>
       </c>
+      <c r="G672">
+        <v>0.7399446798767907</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673">
@@ -11809,6 +13827,9 @@
       <c r="F673">
         <v>-0.01726789853121393</v>
       </c>
+      <c r="G673">
+        <v>-0.01726789853121393</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674">
@@ -11826,6 +13847,9 @@
       <c r="F674">
         <v>0.2085836931366664</v>
       </c>
+      <c r="G674">
+        <v>0.2085836931366664</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675">
@@ -11843,6 +13867,9 @@
       <c r="F675">
         <v>-0.08063669184049885</v>
       </c>
+      <c r="G675">
+        <v>-0.08063669184049885</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676">
@@ -11860,6 +13887,9 @@
       <c r="F676">
         <v>-0.009463775022669251</v>
       </c>
+      <c r="G676">
+        <v>-0.009463775022669251</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677">
@@ -11877,6 +13907,9 @@
       <c r="F677">
         <v>-0.7102163316159741</v>
       </c>
+      <c r="G677">
+        <v>-0.7102163316159741</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678">
@@ -11894,6 +13927,9 @@
       <c r="F678">
         <v>-0.5806972965462118</v>
       </c>
+      <c r="G678">
+        <v>-0.5806972965462118</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679">
@@ -11911,6 +13947,9 @@
       <c r="F679">
         <v>-0.6443071845326257</v>
       </c>
+      <c r="G679">
+        <v>-0.6443071845326257</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680">
@@ -11928,6 +13967,9 @@
       <c r="F680">
         <v>-0.5778628732828717</v>
       </c>
+      <c r="G680">
+        <v>-0.5778628732828717</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681">
@@ -11945,6 +13987,9 @@
       <c r="F681">
         <v>0.1198450740475629</v>
       </c>
+      <c r="G681">
+        <v>0.1198450740475629</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682">
@@ -11962,6 +14007,9 @@
       <c r="F682">
         <v>-0.1578512301567244</v>
       </c>
+      <c r="G682">
+        <v>-0.1578512301567244</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683">
@@ -11979,6 +14027,9 @@
       <c r="F683">
         <v>-0.08754952271063217</v>
       </c>
+      <c r="G683">
+        <v>-0.08754952271063217</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684">
@@ -11996,6 +14047,9 @@
       <c r="F684">
         <v>-0.2361024567856025</v>
       </c>
+      <c r="G684">
+        <v>-0.2361024567856025</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685">
@@ -12013,6 +14067,9 @@
       <c r="F685">
         <v>-0.2931308383082389</v>
       </c>
+      <c r="G685">
+        <v>-0.2931308383082389</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686">
@@ -12030,6 +14087,9 @@
       <c r="F686">
         <v>-0.01189352774304544</v>
       </c>
+      <c r="G686">
+        <v>-0.01189352774304544</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687">
@@ -12047,6 +14107,9 @@
       <c r="F687">
         <v>-0.5242367273010029</v>
       </c>
+      <c r="G687">
+        <v>-0.5242367273010029</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688">
@@ -12064,6 +14127,9 @@
       <c r="F688">
         <v>-0.4308835881250106</v>
       </c>
+      <c r="G688">
+        <v>-0.4308835881250106</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689">
@@ -12081,6 +14147,9 @@
       <c r="F689">
         <v>-0.523643958909161</v>
       </c>
+      <c r="G689">
+        <v>-0.523643958909161</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690">
@@ -12098,6 +14167,9 @@
       <c r="F690">
         <v>-0.4982853115858538</v>
       </c>
+      <c r="G690">
+        <v>-0.4982853115858538</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691">
@@ -12115,6 +14187,9 @@
       <c r="F691">
         <v>-0.1194519136392167</v>
       </c>
+      <c r="G691">
+        <v>-0.1194519136392167</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692">
@@ -12132,6 +14207,9 @@
       <c r="F692">
         <v>-0.1432099769757646</v>
       </c>
+      <c r="G692">
+        <v>-0.1432099769757646</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693">
@@ -12149,6 +14227,9 @@
       <c r="F693">
         <v>-0.8780313662392986</v>
       </c>
+      <c r="G693">
+        <v>-0.8780313662392986</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694">
@@ -12166,6 +14247,9 @@
       <c r="F694">
         <v>-0.2969569928954195</v>
       </c>
+      <c r="G694">
+        <v>-0.2969569928954195</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695">
@@ -12183,6 +14267,9 @@
       <c r="F695">
         <v>-0.7159717575733692</v>
       </c>
+      <c r="G695">
+        <v>-0.7159717575733692</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696">
@@ -12200,6 +14287,9 @@
       <c r="F696">
         <v>-0.4395013720351267</v>
       </c>
+      <c r="G696">
+        <v>-0.4395013720351267</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697">
@@ -12217,6 +14307,9 @@
       <c r="F697">
         <v>0.2202949694656536</v>
       </c>
+      <c r="G697">
+        <v>0.2202949694656536</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698">
@@ -12234,6 +14327,9 @@
       <c r="F698">
         <v>-1.900165857263729</v>
       </c>
+      <c r="G698">
+        <v>-1.900165857263729</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699">
@@ -12251,6 +14347,9 @@
       <c r="F699">
         <v>-0.09315956453175463</v>
       </c>
+      <c r="G699">
+        <v>-0.09315956453175463</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700">
@@ -12268,6 +14367,9 @@
       <c r="F700">
         <v>-1.186742448871411</v>
       </c>
+      <c r="G700">
+        <v>-1.186742448871411</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701">
@@ -12285,6 +14387,9 @@
       <c r="F701">
         <v>-0.0579218846746223</v>
       </c>
+      <c r="G701">
+        <v>-0.0579218846746223</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702">
@@ -12302,6 +14407,9 @@
       <c r="F702">
         <v>-0.2937316417853161</v>
       </c>
+      <c r="G702">
+        <v>-0.2937316417853161</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703">
@@ -12319,6 +14427,9 @@
       <c r="F703">
         <v>-0.3454858222626849</v>
       </c>
+      <c r="G703">
+        <v>-0.3454858222626849</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704">
@@ -12336,6 +14447,9 @@
       <c r="F704">
         <v>-0.4299192683194866</v>
       </c>
+      <c r="G704">
+        <v>-0.4299192683194866</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705">
@@ -12353,6 +14467,9 @@
       <c r="F705">
         <v>-0.4385701546622734</v>
       </c>
+      <c r="G705">
+        <v>-0.4385701546622734</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706">
@@ -12370,6 +14487,9 @@
       <c r="F706">
         <v>0.2616662246400914</v>
       </c>
+      <c r="G706">
+        <v>0.2616662246400914</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707">
@@ -12387,6 +14507,9 @@
       <c r="F707">
         <v>0.5253631109374195</v>
       </c>
+      <c r="G707">
+        <v>0.5253631109374195</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708">
@@ -12404,6 +14527,9 @@
       <c r="F708">
         <v>0.3479696904285772</v>
       </c>
+      <c r="G708">
+        <v>0.3479696904285772</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709">
@@ -12421,6 +14547,9 @@
       <c r="F709">
         <v>0.04398035534216384</v>
       </c>
+      <c r="G709">
+        <v>0.04398035534216384</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710">
@@ -12438,6 +14567,9 @@
       <c r="F710">
         <v>-0.1400581668034298</v>
       </c>
+      <c r="G710">
+        <v>-0.1400581668034298</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711">
@@ -12455,6 +14587,9 @@
       <c r="F711">
         <v>0.1344003170065575</v>
       </c>
+      <c r="G711">
+        <v>0.1344003170065575</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712">
@@ -12472,6 +14607,9 @@
       <c r="F712">
         <v>0.4708406560791873</v>
       </c>
+      <c r="G712">
+        <v>0.4708406560791873</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713">
@@ -12489,6 +14627,9 @@
       <c r="F713">
         <v>0.3769203279210039</v>
       </c>
+      <c r="G713">
+        <v>0.3769203279210039</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714">
@@ -12506,6 +14647,9 @@
       <c r="F714">
         <v>0.2712498623593566</v>
       </c>
+      <c r="G714">
+        <v>0.2712498623593566</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715">
@@ -12523,6 +14667,9 @@
       <c r="F715">
         <v>0.1153740731895358</v>
       </c>
+      <c r="G715">
+        <v>0.1153740731895358</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716">
@@ -12540,6 +14687,9 @@
       <c r="F716">
         <v>0.1089590913949882</v>
       </c>
+      <c r="G716">
+        <v>0.1089590913949882</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717">
@@ -12557,6 +14707,9 @@
       <c r="F717">
         <v>-0.4423866037417634</v>
       </c>
+      <c r="G717">
+        <v>-0.4423866037417634</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718">
@@ -12574,6 +14727,9 @@
       <c r="F718">
         <v>-0.2309542598696623</v>
       </c>
+      <c r="G718">
+        <v>-0.2309542598696623</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719">
@@ -12591,6 +14747,9 @@
       <c r="F719">
         <v>-0.394959146952747</v>
       </c>
+      <c r="G719">
+        <v>-0.394959146952747</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720">
@@ -12608,6 +14767,9 @@
       <c r="F720">
         <v>-0.4007882321879866</v>
       </c>
+      <c r="G720">
+        <v>-0.4007882321879866</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721">
@@ -12625,6 +14787,9 @@
       <c r="F721">
         <v>0.1633753078903566</v>
       </c>
+      <c r="G721">
+        <v>0.1633753078903566</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722">
@@ -12642,6 +14807,9 @@
       <c r="F722">
         <v>0.0699932193843075</v>
       </c>
+      <c r="G722">
+        <v>0.0699932193843075</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723">
@@ -12659,6 +14827,9 @@
       <c r="F723">
         <v>0.2006089180810341</v>
       </c>
+      <c r="G723">
+        <v>0.2006089180810341</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724">
@@ -12676,6 +14847,9 @@
       <c r="F724">
         <v>-0.004481520060468903</v>
       </c>
+      <c r="G724">
+        <v>-0.004481520060468903</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725">
@@ -12693,6 +14867,9 @@
       <c r="F725">
         <v>-0.09456257893255317</v>
       </c>
+      <c r="G725">
+        <v>-0.09456257893255317</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726">
@@ -12710,6 +14887,9 @@
       <c r="F726">
         <v>-0.0232391866963849</v>
       </c>
+      <c r="G726">
+        <v>-0.0232391866963849</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727">
@@ -12727,6 +14907,9 @@
       <c r="F727">
         <v>-0.6643174426971254</v>
       </c>
+      <c r="G727">
+        <v>-0.6643174426971254</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728">
@@ -12744,6 +14927,9 @@
       <c r="F728">
         <v>-0.5296834370931013</v>
       </c>
+      <c r="G728">
+        <v>-0.5296834370931013</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729">
@@ -12761,6 +14947,9 @@
       <c r="F729">
         <v>-0.6027249212052755</v>
       </c>
+      <c r="G729">
+        <v>-0.6027249212052755</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730">
@@ -12778,6 +14967,9 @@
       <c r="F730">
         <v>-0.5505896788097147</v>
       </c>
+      <c r="G730">
+        <v>-0.5505896788097147</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731">
@@ -12795,6 +14987,9 @@
       <c r="F731">
         <v>0.1201977214231988</v>
       </c>
+      <c r="G731">
+        <v>0.1201977214231988</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732">
@@ -12812,6 +15007,9 @@
       <c r="F732">
         <v>0.2193320918394615</v>
       </c>
+      <c r="G732">
+        <v>0.2193320918394615</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733">
@@ -12829,6 +15027,9 @@
       <c r="F733">
         <v>0.2705636133370068</v>
       </c>
+      <c r="G733">
+        <v>0.2705636133370068</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734">
@@ -12846,6 +15047,9 @@
       <c r="F734">
         <v>0.1067650308767599</v>
       </c>
+      <c r="G734">
+        <v>0.1067650308767599</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735">
@@ -12863,6 +15067,9 @@
       <c r="F735">
         <v>-0.01492426691498984</v>
       </c>
+      <c r="G735">
+        <v>-0.01492426691498984</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736">
@@ -12880,6 +15087,9 @@
       <c r="F736">
         <v>0.138040729440094</v>
       </c>
+      <c r="G736">
+        <v>0.138040729440094</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737">
@@ -12897,6 +15107,9 @@
       <c r="F737">
         <v>0.4600776184731554</v>
       </c>
+      <c r="G737">
+        <v>0.4600776184731554</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738">
@@ -12914,6 +15127,9 @@
       <c r="F738">
         <v>0.4642645398568889</v>
       </c>
+      <c r="G738">
+        <v>0.4642645398568889</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739">
@@ -12931,6 +15147,9 @@
       <c r="F739">
         <v>0.3151069106678274</v>
       </c>
+      <c r="G739">
+        <v>0.3151069106678274</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740">
@@ -12948,6 +15167,9 @@
       <c r="F740">
         <v>0.1748687760300595</v>
       </c>
+      <c r="G740">
+        <v>0.1748687760300595</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741">
@@ -12965,6 +15187,9 @@
       <c r="F741">
         <v>0.2563377234410432</v>
       </c>
+      <c r="G741">
+        <v>0.2563377234410432</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742">
@@ -12982,6 +15207,9 @@
       <c r="F742">
         <v>0.5288062515116027</v>
       </c>
+      <c r="G742">
+        <v>0.5288062515116027</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743">
@@ -12999,6 +15227,9 @@
       <c r="F743">
         <v>0.6686955773823922</v>
       </c>
+      <c r="G743">
+        <v>0.6686955773823922</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744">
@@ -13016,6 +15247,9 @@
       <c r="F744">
         <v>0.5181497843447571</v>
       </c>
+      <c r="G744">
+        <v>0.5181497843447571</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745">
@@ -13033,6 +15267,9 @@
       <c r="F745">
         <v>0.3846473863416709</v>
       </c>
+      <c r="G745">
+        <v>0.3846473863416709</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746">
@@ -13050,6 +15287,9 @@
       <c r="F746">
         <v>-0.1607188067418369</v>
       </c>
+      <c r="G746">
+        <v>-0.1607188067418369</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747">
@@ -13067,6 +15307,9 @@
       <c r="F747">
         <v>-0.8962808441407409</v>
       </c>
+      <c r="G747">
+        <v>-0.8962808441407409</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748">
@@ -13084,6 +15327,9 @@
       <c r="F748">
         <v>-0.7227316956693322</v>
       </c>
+      <c r="G748">
+        <v>-0.7227316956693322</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749">
@@ -13101,6 +15347,9 @@
       <c r="F749">
         <v>-0.7410729514064097</v>
       </c>
+      <c r="G749">
+        <v>-0.7410729514064097</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750">
@@ -13118,6 +15367,9 @@
       <c r="F750">
         <v>-0.641304256202794</v>
       </c>
+      <c r="G750">
+        <v>-0.641304256202794</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751">
@@ -13135,6 +15387,9 @@
       <c r="F751">
         <v>0.293120266904685</v>
       </c>
+      <c r="G751">
+        <v>0.293120266904685</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752">
@@ -13152,6 +15407,9 @@
       <c r="F752">
         <v>1.491286705514029</v>
       </c>
+      <c r="G752">
+        <v>1.491286705514029</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753">
@@ -13169,6 +15427,9 @@
       <c r="F753">
         <v>1.64057955679134</v>
       </c>
+      <c r="G753">
+        <v>1.64057955679134</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754">
@@ -13186,6 +15447,9 @@
       <c r="F754">
         <v>2.056851745805938</v>
       </c>
+      <c r="G754">
+        <v>2.056851745805938</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755">
@@ -13203,6 +15467,9 @@
       <c r="F755">
         <v>2.892438731522593</v>
       </c>
+      <c r="G755">
+        <v>2.892438731522593</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756">
@@ -13220,6 +15487,9 @@
       <c r="F756">
         <v>-0.03827886226072016</v>
       </c>
+      <c r="G756">
+        <v>-0.03827886226072016</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757">
@@ -13237,6 +15507,9 @@
       <c r="F757">
         <v>-0.7863015489303444</v>
       </c>
+      <c r="G757">
+        <v>-0.7863015489303444</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758">
@@ -13254,6 +15527,9 @@
       <c r="F758">
         <v>-0.628802085593381</v>
       </c>
+      <c r="G758">
+        <v>-0.628802085593381</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759">
@@ -13271,6 +15547,9 @@
       <c r="F759">
         <v>-0.6787932406243365</v>
       </c>
+      <c r="G759">
+        <v>-0.6787932406243365</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760">
@@ -13288,6 +15567,9 @@
       <c r="F760">
         <v>-0.5996045078732081</v>
       </c>
+      <c r="G760">
+        <v>-0.5996045078732081</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761">
@@ -13305,6 +15587,9 @@
       <c r="F761">
         <v>0.06669735836628082</v>
       </c>
+      <c r="G761">
+        <v>0.06669735836628082</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762">
@@ -13322,6 +15607,9 @@
       <c r="F762">
         <v>-0.700560531234606</v>
       </c>
+      <c r="G762">
+        <v>-0.700560531234606</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763">
@@ -13339,6 +15627,9 @@
       <c r="F763">
         <v>-0.4611586290786251</v>
       </c>
+      <c r="G763">
+        <v>-0.4611586290786251</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764">
@@ -13356,6 +15647,9 @@
       <c r="F764">
         <v>-0.5706330011043003</v>
       </c>
+      <c r="G764">
+        <v>-0.5706330011043003</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765">
@@ -13373,6 +15667,9 @@
       <c r="F765">
         <v>-0.5255366739724965</v>
       </c>
+      <c r="G765">
+        <v>-0.5255366739724965</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766">
@@ -13390,6 +15687,9 @@
       <c r="F766">
         <v>0.04262451986435788</v>
       </c>
+      <c r="G766">
+        <v>0.04262451986435788</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767">
@@ -13407,6 +15707,9 @@
       <c r="F767">
         <v>-0.6820968263797663</v>
       </c>
+      <c r="G767">
+        <v>-0.6820968263797663</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768">
@@ -13424,6 +15727,9 @@
       <c r="F768">
         <v>-0.720326682239952</v>
       </c>
+      <c r="G768">
+        <v>-0.720326682239952</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769">
@@ -13441,6 +15747,9 @@
       <c r="F769">
         <v>-0.8430767092374862</v>
       </c>
+      <c r="G769">
+        <v>-0.8430767092374862</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770">
@@ -13458,6 +15767,9 @@
       <c r="F770">
         <v>-0.7450589197965779</v>
       </c>
+      <c r="G770">
+        <v>-0.7450589197965779</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771">
@@ -13475,6 +15787,9 @@
       <c r="F771">
         <v>0.1720539694069549</v>
       </c>
+      <c r="G771">
+        <v>0.1720539694069549</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772">
@@ -13492,6 +15807,9 @@
       <c r="F772">
         <v>0.4439219861361376</v>
       </c>
+      <c r="G772">
+        <v>0.4439219861361376</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773">
@@ -13509,6 +15827,9 @@
       <c r="F773">
         <v>0.4989675787497081</v>
       </c>
+      <c r="G773">
+        <v>0.4989675787497081</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774">
@@ -13526,6 +15847,9 @@
       <c r="F774">
         <v>0.3473895229775485</v>
       </c>
+      <c r="G774">
+        <v>0.3473895229775485</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775">
@@ -13543,6 +15867,9 @@
       <c r="F775">
         <v>0.2067687803917836</v>
       </c>
+      <c r="G775">
+        <v>0.2067687803917836</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776">
@@ -13560,6 +15887,9 @@
       <c r="F776">
         <v>-0.03402193525734263</v>
       </c>
+      <c r="G776">
+        <v>-0.03402193525734263</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777">
@@ -13577,6 +15907,9 @@
       <c r="F777">
         <v>-0.4943894577664664</v>
       </c>
+      <c r="G777">
+        <v>-0.4943894577664664</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778">
@@ -13594,6 +15927,9 @@
       <c r="F778">
         <v>-0.3534939468776426</v>
       </c>
+      <c r="G778">
+        <v>-0.3534939468776426</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779">
@@ -13611,6 +15947,9 @@
       <c r="F779">
         <v>-0.4559271399829444</v>
       </c>
+      <c r="G779">
+        <v>-0.4559271399829444</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780">
@@ -13628,6 +15967,9 @@
       <c r="F780">
         <v>-0.451084801783545</v>
       </c>
+      <c r="G780">
+        <v>-0.451084801783545</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781">
@@ -13645,6 +15987,9 @@
       <c r="F781">
         <v>0.6540410944088557</v>
       </c>
+      <c r="G781">
+        <v>0.6540410944088557</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782">
@@ -13662,6 +16007,9 @@
       <c r="F782">
         <v>5.703526679568335</v>
       </c>
+      <c r="G782">
+        <v>4</v>
+      </c>
     </row>
     <row r="783">
       <c r="A783">
@@ -13679,6 +16027,9 @@
       <c r="F783">
         <v>5.85515416311088</v>
       </c>
+      <c r="G783">
+        <v>4</v>
+      </c>
     </row>
     <row r="784">
       <c r="A784">
@@ -13696,6 +16047,9 @@
       <c r="F784">
         <v>0.8952621680420633</v>
       </c>
+      <c r="G784">
+        <v>0.8952621680420633</v>
+      </c>
     </row>
     <row r="785">
       <c r="A785">
@@ -13713,6 +16067,9 @@
       <c r="F785">
         <v>1.351871729601891</v>
       </c>
+      <c r="G785">
+        <v>1.351871729601891</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786">
@@ -13730,6 +16087,9 @@
       <c r="F786">
         <v>1.629220850019745</v>
       </c>
+      <c r="G786">
+        <v>1.629220850019745</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787">
@@ -13747,6 +16107,9 @@
       <c r="F787">
         <v>1.92409534458239</v>
       </c>
+      <c r="G787">
+        <v>1.92409534458239</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788">
@@ -13764,6 +16127,9 @@
       <c r="F788">
         <v>2.626424038068257</v>
       </c>
+      <c r="G788">
+        <v>2.626424038068257</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789">
@@ -13781,6 +16147,9 @@
       <c r="F789">
         <v>-0.2378478781070089</v>
       </c>
+      <c r="G789">
+        <v>-0.2378478781070089</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790">
@@ -13798,6 +16167,9 @@
       <c r="F790">
         <v>0.4319702696128657</v>
       </c>
+      <c r="G790">
+        <v>0.4319702696128657</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791">
@@ -13815,6 +16187,9 @@
       <c r="F791">
         <v>-1.049922456729122</v>
       </c>
+      <c r="G791">
+        <v>-1.049922456729122</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792">
@@ -13832,6 +16207,9 @@
       <c r="F792">
         <v>-0.05841232881474657</v>
       </c>
+      <c r="G792">
+        <v>-0.05841232881474657</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793">
@@ -13849,6 +16227,9 @@
       <c r="F793">
         <v>-0.7128656230476965</v>
       </c>
+      <c r="G793">
+        <v>-0.7128656230476965</v>
+      </c>
     </row>
     <row r="794">
       <c r="A794">
@@ -13866,6 +16247,9 @@
       <c r="F794">
         <v>1.09534781830457</v>
       </c>
+      <c r="G794">
+        <v>1.09534781830457</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795">
@@ -13883,6 +16267,9 @@
       <c r="F795">
         <v>1.147225785635178</v>
       </c>
+      <c r="G795">
+        <v>1.147225785635178</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796">
@@ -13900,6 +16287,9 @@
       <c r="F796">
         <v>2.680551426599325</v>
       </c>
+      <c r="G796">
+        <v>2.680551426599325</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797">
@@ -13917,6 +16307,9 @@
       <c r="F797">
         <v>2.789132056630197</v>
       </c>
+      <c r="G797">
+        <v>2.789132056630197</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798">
@@ -13934,6 +16327,9 @@
       <c r="F798">
         <v>3.092988736506623</v>
       </c>
+      <c r="G798">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="799">
       <c r="A799">
@@ -13951,6 +16347,9 @@
       <c r="F799">
         <v>1.169814223277117</v>
       </c>
+      <c r="G799">
+        <v>1.169814223277117</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800">
@@ -13968,6 +16367,9 @@
       <c r="F800">
         <v>0.5501460092084582</v>
       </c>
+      <c r="G800">
+        <v>0.5501460092084582</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801">
@@ -13985,6 +16387,9 @@
       <c r="F801">
         <v>0.591507499670335</v>
       </c>
+      <c r="G801">
+        <v>0.591507499670335</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802">
@@ -14002,6 +16407,9 @@
       <c r="F802">
         <v>0.4584552959198168</v>
       </c>
+      <c r="G802">
+        <v>0.4584552959198168</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803">
@@ -14019,6 +16427,9 @@
       <c r="F803">
         <v>0.3145402844036796</v>
       </c>
+      <c r="G803">
+        <v>0.3145402844036796</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804">
@@ -14036,6 +16447,9 @@
       <c r="F804">
         <v>0.06330720445318566</v>
       </c>
+      <c r="G804">
+        <v>0.06330720445318566</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805">
@@ -14053,6 +16467,9 @@
       <c r="F805">
         <v>-0.9771521665738032</v>
       </c>
+      <c r="G805">
+        <v>-0.9771521665738032</v>
+      </c>
     </row>
     <row r="806">
       <c r="A806">
@@ -14070,6 +16487,9 @@
       <c r="F806">
         <v>-0.2288238465962527</v>
       </c>
+      <c r="G806">
+        <v>-0.2288238465962527</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807">
@@ -14087,6 +16507,9 @@
       <c r="F807">
         <v>-0.8006675813066559</v>
       </c>
+      <c r="G807">
+        <v>-0.8006675813066559</v>
+      </c>
     </row>
     <row r="808">
       <c r="A808">
@@ -14104,6 +16527,9 @@
       <c r="F808">
         <v>-0.3940274873578175</v>
       </c>
+      <c r="G808">
+        <v>-0.3940274873578175</v>
+      </c>
     </row>
     <row r="809">
       <c r="A809">
@@ -14121,6 +16547,9 @@
       <c r="F809">
         <v>0.1199539799091252</v>
       </c>
+      <c r="G809">
+        <v>0.1199539799091252</v>
+      </c>
     </row>
     <row r="810">
       <c r="A810">
@@ -14138,6 +16567,9 @@
       <c r="F810">
         <v>0.7327805181913418</v>
       </c>
+      <c r="G810">
+        <v>0.7327805181913418</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811">
@@ -14155,6 +16587,9 @@
       <c r="F811">
         <v>2.898282122206162</v>
       </c>
+      <c r="G811">
+        <v>2.898282122206162</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812">
@@ -14172,6 +16607,9 @@
       <c r="F812">
         <v>1.877802867611431</v>
       </c>
+      <c r="G812">
+        <v>1.877802867611431</v>
+      </c>
     </row>
     <row r="813">
       <c r="A813">
@@ -14189,6 +16627,9 @@
       <c r="F813">
         <v>3.092988736506623</v>
       </c>
+      <c r="G813">
+        <v>3.092988736506623</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814">
@@ -14206,6 +16647,9 @@
       <c r="F814">
         <v>0.03916871696704145</v>
       </c>
+      <c r="G814">
+        <v>0.03916871696704145</v>
+      </c>
     </row>
     <row r="815">
       <c r="A815">
@@ -14223,6 +16667,9 @@
       <c r="F815">
         <v>-0.4035162330121322</v>
       </c>
+      <c r="G815">
+        <v>-0.4035162330121322</v>
+      </c>
     </row>
     <row r="816">
       <c r="A816">
@@ -14240,6 +16687,9 @@
       <c r="F816">
         <v>-0.3161182437347962</v>
       </c>
+      <c r="G816">
+        <v>-0.3161182437347962</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817">
@@ -14257,6 +16707,9 @@
       <c r="F817">
         <v>-0.4319310070727911</v>
       </c>
+      <c r="G817">
+        <v>-0.4319310070727911</v>
+      </c>
     </row>
     <row r="818">
       <c r="A818">
@@ -14274,6 +16727,9 @@
       <c r="F818">
         <v>-0.4352588326514193</v>
       </c>
+      <c r="G818">
+        <v>-0.4352588326514193</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819">
@@ -14291,6 +16747,9 @@
       <c r="F819">
         <v>-0.1653551419005939</v>
       </c>
+      <c r="G819">
+        <v>-0.1653551419005939</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820">
@@ -14308,6 +16767,9 @@
       <c r="F820">
         <v>-0.04032474476094012</v>
       </c>
+      <c r="G820">
+        <v>-0.04032474476094012</v>
+      </c>
     </row>
     <row r="821">
       <c r="A821">
@@ -14325,6 +16787,9 @@
       <c r="F821">
         <v>-0.0748887835079729</v>
       </c>
+      <c r="G821">
+        <v>-0.0748887835079729</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822">
@@ -14342,6 +16807,9 @@
       <c r="F822">
         <v>-0.1848692116565305</v>
       </c>
+      <c r="G822">
+        <v>-0.1848692116565305</v>
+      </c>
     </row>
     <row r="823">
       <c r="A823">
@@ -14359,6 +16827,9 @@
       <c r="F823">
         <v>-0.2699787619682064</v>
       </c>
+      <c r="G823">
+        <v>-0.2699787619682064</v>
+      </c>
     </row>
     <row r="824">
       <c r="A824">
@@ -14376,6 +16847,9 @@
       <c r="F824">
         <v>-0.02867866073962849</v>
       </c>
+      <c r="G824">
+        <v>-0.02867866073962849</v>
+      </c>
     </row>
     <row r="825">
       <c r="A825">
@@ -14393,6 +16867,9 @@
       <c r="F825">
         <v>-0.5052528049402978</v>
       </c>
+      <c r="G825">
+        <v>-0.5052528049402978</v>
+      </c>
     </row>
     <row r="826">
       <c r="A826">
@@ -14410,6 +16887,9 @@
       <c r="F826">
         <v>-0.402578805056657</v>
       </c>
+      <c r="G826">
+        <v>-0.402578805056657</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827">
@@ -14427,6 +16907,9 @@
       <c r="F827">
         <v>-0.5023123029335331</v>
       </c>
+      <c r="G827">
+        <v>-0.5023123029335331</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828">
@@ -14444,6 +16927,9 @@
       <c r="F828">
         <v>-0.4837390410456064</v>
       </c>
+      <c r="G828">
+        <v>-0.4837390410456064</v>
+      </c>
     </row>
     <row r="829">
       <c r="A829">
@@ -14461,6 +16947,9 @@
       <c r="F829">
         <v>0.2407695723405806</v>
       </c>
+      <c r="G829">
+        <v>0.2407695723405806</v>
+      </c>
     </row>
     <row r="830">
       <c r="A830">
@@ -14478,6 +16967,9 @@
       <c r="F830">
         <v>0.01620836136284283</v>
       </c>
+      <c r="G830">
+        <v>0.01620836136284283</v>
+      </c>
     </row>
     <row r="831">
       <c r="A831">
@@ -14495,6 +16987,9 @@
       <c r="F831">
         <v>0.2645959227044166</v>
       </c>
+      <c r="G831">
+        <v>0.2645959227044166</v>
+      </c>
     </row>
     <row r="832">
       <c r="A832">
@@ -14512,6 +17007,9 @@
       <c r="F832">
         <v>0.04110865251289113</v>
       </c>
+      <c r="G832">
+        <v>0.04110865251289113</v>
+      </c>
     </row>
     <row r="833">
       <c r="A833">
@@ -14529,6 +17027,9 @@
       <c r="F833">
         <v>-0.05738985713554898</v>
       </c>
+      <c r="G833">
+        <v>-0.05738985713554898</v>
+      </c>
     </row>
     <row r="834">
       <c r="A834">
@@ -14546,6 +17047,9 @@
       <c r="F834">
         <v>-0.1687270770514331</v>
       </c>
+      <c r="G834">
+        <v>-0.1687270770514331</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835">
@@ -14563,6 +17067,9 @@
       <c r="F835">
         <v>-0.8703968215038117</v>
       </c>
+      <c r="G835">
+        <v>-0.8703968215038117</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836">
@@ -14580,6 +17087,9 @@
       <c r="F836">
         <v>-0.6887558737688643</v>
       </c>
+      <c r="G836">
+        <v>-0.6887558737688643</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837">
@@ -14597,6 +17107,9 @@
       <c r="F837">
         <v>-0.7229667560655869</v>
       </c>
+      <c r="G837">
+        <v>-0.7229667560655869</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838">
@@ -14614,6 +17127,9 @@
       <c r="F838">
         <v>-0.6273588513945744</v>
       </c>
+      <c r="G838">
+        <v>-0.6273588513945744</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839">
@@ -14631,6 +17147,9 @@
       <c r="F839">
         <v>-0.06381376179383179</v>
       </c>
+      <c r="G839">
+        <v>-0.06381376179383179</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840">
@@ -14648,6 +17167,9 @@
       <c r="F840">
         <v>0.6335902026281222</v>
       </c>
+      <c r="G840">
+        <v>0.6335902026281222</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841">
@@ -14665,6 +17187,9 @@
       <c r="F841">
         <v>0.02129626774049994</v>
       </c>
+      <c r="G841">
+        <v>0.02129626774049994</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842">
@@ -14682,6 +17207,9 @@
       <c r="F842">
         <v>0.1395630611173801</v>
       </c>
+      <c r="G842">
+        <v>0.1395630611173801</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843">
@@ -14699,6 +17227,9 @@
       <c r="F843">
         <v>-0.08575759158525816</v>
       </c>
+      <c r="G843">
+        <v>-0.08575759158525816</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844">
@@ -14716,6 +17247,9 @@
       <c r="F844">
         <v>-0.02615599152378141</v>
       </c>
+      <c r="G844">
+        <v>-0.02615599152378141</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845">
@@ -14733,6 +17267,9 @@
       <c r="F845">
         <v>-0.4284509417414347</v>
       </c>
+      <c r="G845">
+        <v>-0.4284509417414347</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846">
@@ -14750,6 +17287,9 @@
       <c r="F846">
         <v>-0.3050560586017811</v>
       </c>
+      <c r="G846">
+        <v>-0.3050560586017811</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847">
@@ -14767,6 +17307,9 @@
       <c r="F847">
         <v>-0.418363528511114</v>
       </c>
+      <c r="G847">
+        <v>-0.418363528511114</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848">
@@ -14784,6 +17327,9 @@
       <c r="F848">
         <v>-0.4254036730910296</v>
       </c>
+      <c r="G848">
+        <v>-0.4254036730910296</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849">
@@ -14801,6 +17347,9 @@
       <c r="F849">
         <v>0.1578699832754645</v>
       </c>
+      <c r="G849">
+        <v>0.1578699832754645</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850">
@@ -14818,6 +17367,9 @@
       <c r="F850">
         <v>-0.04164080407114772</v>
       </c>
+      <c r="G850">
+        <v>-0.04164080407114772</v>
+      </c>
     </row>
     <row r="851">
       <c r="A851">
@@ -14835,6 +17387,9 @@
       <c r="F851">
         <v>-0.009573807854296472</v>
       </c>
+      <c r="G851">
+        <v>-0.009573807854296472</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852">
@@ -14852,6 +17407,9 @@
       <c r="F852">
         <v>-0.1648247421271463</v>
       </c>
+      <c r="G852">
+        <v>-0.1648247421271463</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853">
@@ -14869,6 +17427,9 @@
       <c r="F853">
         <v>-0.2386605450152932</v>
       </c>
+      <c r="G853">
+        <v>-0.2386605450152932</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854">
@@ -14886,6 +17447,9 @@
       <c r="F854">
         <v>-0.2904614031864545</v>
       </c>
+      <c r="G854">
+        <v>-0.2904614031864545</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855">
@@ -14903,6 +17467,9 @@
       <c r="F855">
         <v>-0.03020512821460835</v>
       </c>
+      <c r="G855">
+        <v>-0.03020512821460835</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856">
@@ -14920,6 +17487,9 @@
       <c r="F856">
         <v>-0.4963895052623949</v>
       </c>
+      <c r="G856">
+        <v>-0.4963895052623949</v>
+      </c>
     </row>
     <row r="857">
       <c r="A857">
@@ -14937,6 +17507,9 @@
       <c r="F857">
         <v>-0.4377041440245418</v>
       </c>
+      <c r="G857">
+        <v>-0.4377041440245418</v>
+      </c>
     </row>
     <row r="858">
       <c r="A858">
@@ -14954,6 +17527,9 @@
       <c r="F858">
         <v>-0.4721003585274006</v>
       </c>
+      <c r="G858">
+        <v>-0.4721003585274006</v>
+      </c>
     </row>
     <row r="859">
       <c r="A859">
@@ -14971,6 +17547,9 @@
       <c r="F859">
         <v>0.03388816926444226</v>
       </c>
+      <c r="G859">
+        <v>0.03388816926444226</v>
+      </c>
     </row>
     <row r="860">
       <c r="A860">
@@ -14988,6 +17567,9 @@
       <c r="F860">
         <v>-0.85206641960512</v>
       </c>
+      <c r="G860">
+        <v>-0.85206641960512</v>
+      </c>
     </row>
     <row r="861">
       <c r="A861">
@@ -15005,6 +17587,9 @@
       <c r="F861">
         <v>-0.5778942317603946</v>
       </c>
+      <c r="G861">
+        <v>-0.5778942317603946</v>
+      </c>
     </row>
     <row r="862">
       <c r="A862">
@@ -15022,6 +17607,9 @@
       <c r="F862">
         <v>-0.6616765835634334</v>
       </c>
+      <c r="G862">
+        <v>-0.6616765835634334</v>
+      </c>
     </row>
     <row r="863">
       <c r="A863">
@@ -15039,6 +17627,9 @@
       <c r="F863">
         <v>-0.5845359223664824</v>
       </c>
+      <c r="G863">
+        <v>-0.5845359223664824</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864">
@@ -15056,6 +17647,9 @@
       <c r="F864">
         <v>-0.01189130821017519</v>
       </c>
+      <c r="G864">
+        <v>-0.01189130821017519</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865">
@@ -15073,6 +17667,9 @@
       <c r="F865">
         <v>-0.6364433893585311</v>
       </c>
+      <c r="G865">
+        <v>-0.6364433893585311</v>
+      </c>
     </row>
     <row r="866">
       <c r="A866">
@@ -15090,6 +17687,9 @@
       <c r="F866">
         <v>-0.5085591673899365</v>
       </c>
+      <c r="G866">
+        <v>-0.5085591673899365</v>
+      </c>
     </row>
     <row r="867">
       <c r="A867">
@@ -15107,6 +17707,9 @@
       <c r="F867">
         <v>-0.5863428229136655</v>
       </c>
+      <c r="G867">
+        <v>-0.5863428229136655</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868">
@@ -15124,6 +17727,9 @@
       <c r="F868">
         <v>-0.5398588618860397</v>
       </c>
+      <c r="G868">
+        <v>-0.5398588618860397</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869">
@@ -15141,6 +17747,9 @@
       <c r="F869">
         <v>-0.004839105807658453</v>
       </c>
+      <c r="G869">
+        <v>-0.004839105807658453</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870">
@@ -15158,6 +17767,9 @@
       <c r="F870">
         <v>-0.6188942021277951</v>
       </c>
+      <c r="G870">
+        <v>-0.6188942021277951</v>
+      </c>
     </row>
     <row r="871">
       <c r="A871">
@@ -15175,6 +17787,9 @@
       <c r="F871">
         <v>-0.494247277109507</v>
       </c>
+      <c r="G871">
+        <v>-0.494247277109507</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872">
@@ -15192,6 +17807,9 @@
       <c r="F872">
         <v>-0.5751694840443519</v>
       </c>
+      <c r="G872">
+        <v>-0.5751694840443519</v>
+      </c>
     </row>
     <row r="873">
       <c r="A873">
@@ -15209,6 +17827,9 @@
       <c r="F873">
         <v>-0.5325004560810469</v>
       </c>
+      <c r="G873">
+        <v>-0.5325004560810469</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874">
@@ -15226,6 +17847,9 @@
       <c r="F874">
         <v>0.4027277619600012</v>
       </c>
+      <c r="G874">
+        <v>0.4027277619600012</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875">
@@ -15243,6 +17867,9 @@
       <c r="F875">
         <v>1.141218047803482</v>
       </c>
+      <c r="G875">
+        <v>1.141218047803482</v>
+      </c>
     </row>
     <row r="876">
       <c r="A876">
@@ -15260,6 +17887,9 @@
       <c r="F876">
         <v>1.578743746075404</v>
       </c>
+      <c r="G876">
+        <v>1.578743746075404</v>
+      </c>
     </row>
     <row r="877">
       <c r="A877">
@@ -15277,6 +17907,9 @@
       <c r="F877">
         <v>1.756154320778406</v>
       </c>
+      <c r="G877">
+        <v>1.756154320778406</v>
+      </c>
     </row>
     <row r="878">
       <c r="A878">
@@ -15294,6 +17927,9 @@
       <c r="F878">
         <v>2.269978366978601</v>
       </c>
+      <c r="G878">
+        <v>2.269978366978601</v>
+      </c>
     </row>
     <row r="879">
       <c r="A879">
@@ -15311,6 +17947,9 @@
       <c r="F879">
         <v>-0.1075501510380615</v>
       </c>
+      <c r="G879">
+        <v>-0.1075501510380615</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880">
@@ -15328,6 +17967,9 @@
       <c r="F880">
         <v>-0.8815761568462104</v>
       </c>
+      <c r="G880">
+        <v>-0.8815761568462104</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881">
@@ -15345,6 +17987,9 @@
       <c r="F881">
         <v>-0.6970007923811562</v>
       </c>
+      <c r="G881">
+        <v>-0.6970007923811562</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882">
@@ -15362,6 +18007,9 @@
       <c r="F882">
         <v>-0.7290178633297595</v>
       </c>
+      <c r="G882">
+        <v>-0.7290178633297595</v>
+      </c>
     </row>
     <row r="883">
       <c r="A883">
@@ -15379,6 +18027,9 @@
       <c r="F883">
         <v>-0.6311279522575827</v>
       </c>
+      <c r="G883">
+        <v>-0.6311279522575827</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884">
@@ -15396,6 +18047,9 @@
       <c r="F884">
         <v>0.1777538102745107</v>
       </c>
+      <c r="G884">
+        <v>0.1777538102745107</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885">
@@ -15413,6 +18067,9 @@
       <c r="F885">
         <v>0.248140493704617</v>
       </c>
+      <c r="G885">
+        <v>0.248140493704617</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886">
@@ -15430,6 +18087,9 @@
       <c r="F886">
         <v>0.3036285615427456</v>
       </c>
+      <c r="G886">
+        <v>0.3036285615427456</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887">
@@ -15447,6 +18107,9 @@
       <c r="F887">
         <v>0.1369621920001525</v>
       </c>
+      <c r="G887">
+        <v>0.1369621920001525</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888">
@@ -15464,6 +18127,9 @@
       <c r="F888">
         <v>0.01189094138664111</v>
       </c>
+      <c r="G888">
+        <v>0.01189094138664111</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889">
@@ -15481,6 +18147,9 @@
       <c r="F889">
         <v>-0.05739663187395933</v>
       </c>
+      <c r="G889">
+        <v>-0.05739663187395933</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890">
@@ -15498,6 +18167,9 @@
       <c r="F890">
         <v>-0.453501833715668</v>
       </c>
+      <c r="G890">
+        <v>-0.453501833715668</v>
+      </c>
     </row>
     <row r="891">
       <c r="A891">
@@ -15515,6 +18187,9 @@
       <c r="F891">
         <v>-0.6227362166078348</v>
       </c>
+      <c r="G891">
+        <v>-0.6227362166078348</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892">
@@ -15532,6 +18207,9 @@
       <c r="F892">
         <v>-0.5065340279950775</v>
       </c>
+      <c r="G892">
+        <v>-0.5065340279950775</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893">
@@ -15549,6 +18227,9 @@
       <c r="F893">
         <v>-0.5792055863772564</v>
       </c>
+      <c r="G893">
+        <v>-0.5792055863772564</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894">
@@ -15566,6 +18247,9 @@
       <c r="F894">
         <v>0.02486489690832631</v>
       </c>
+      <c r="G894">
+        <v>0.02486489690832631</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895">
@@ -15583,6 +18267,9 @@
       <c r="F895">
         <v>-0.5752291761618585</v>
       </c>
+      <c r="G895">
+        <v>-0.5752291761618585</v>
+      </c>
     </row>
     <row r="896">
       <c r="A896">
@@ -15600,6 +18287,9 @@
       <c r="F896">
         <v>-0.4395268276228259</v>
       </c>
+      <c r="G896">
+        <v>-0.4395268276228259</v>
+      </c>
     </row>
     <row r="897">
       <c r="A897">
@@ -15617,6 +18307,9 @@
       <c r="F897">
         <v>-0.5355143284310498</v>
       </c>
+      <c r="G897">
+        <v>-0.5355143284310498</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898">
@@ -15634,6 +18327,9 @@
       <c r="F898">
         <v>-0.505591085210219</v>
       </c>
+      <c r="G898">
+        <v>-0.505591085210219</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899">
@@ -15651,6 +18347,9 @@
       <c r="F899">
         <v>-0.116857794790272</v>
       </c>
+      <c r="G899">
+        <v>-0.116857794790272</v>
+      </c>
     </row>
     <row r="900">
       <c r="A900">
@@ -15668,6 +18367,9 @@
       <c r="F900">
         <v>-0.8798093501776426</v>
       </c>
+      <c r="G900">
+        <v>-0.8798093501776426</v>
+      </c>
     </row>
     <row r="901">
       <c r="A901">
@@ -15685,6 +18387,9 @@
       <c r="F901">
         <v>-0.6965873793071974</v>
       </c>
+      <c r="G901">
+        <v>-0.6965873793071974</v>
+      </c>
     </row>
     <row r="902">
       <c r="A902">
@@ -15702,6 +18407,9 @@
       <c r="F902">
         <v>-0.7285083029898499</v>
       </c>
+      <c r="G902">
+        <v>-0.7285083029898499</v>
+      </c>
     </row>
     <row r="903">
       <c r="A903">
@@ -15719,6 +18427,9 @@
       <c r="F903">
         <v>-0.630872387173796</v>
       </c>
+      <c r="G903">
+        <v>-0.630872387173796</v>
+      </c>
     </row>
     <row r="904">
       <c r="A904">
@@ -15736,6 +18447,9 @@
       <c r="F904">
         <v>-0.1487811456056269</v>
       </c>
+      <c r="G904">
+        <v>-0.1487811456056269</v>
+      </c>
     </row>
     <row r="905">
       <c r="A905">
@@ -15753,6 +18467,9 @@
       <c r="F905">
         <v>-1.15086095015741</v>
       </c>
+      <c r="G905">
+        <v>-1.15086095015741</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906">
@@ -15770,6 +18487,9 @@
       <c r="F906">
         <v>-0.8843283556225839</v>
       </c>
+      <c r="G906">
+        <v>-0.8843283556225839</v>
+      </c>
     </row>
     <row r="907">
       <c r="A907">
@@ -15787,6 +18507,9 @@
       <c r="F907">
         <v>-0.8623265969292262</v>
       </c>
+      <c r="G907">
+        <v>-0.8623265969292262</v>
+      </c>
     </row>
     <row r="908">
       <c r="A908">
@@ -15804,6 +18527,9 @@
       <c r="F908">
         <v>-0.7120922563156791</v>
       </c>
+      <c r="G908">
+        <v>-0.7120922563156791</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909">
@@ -15821,6 +18547,9 @@
       <c r="F909">
         <v>0.05129176582423145</v>
       </c>
+      <c r="G909">
+        <v>0.05129176582423145</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910">
@@ -15838,6 +18567,9 @@
       <c r="F910">
         <v>-0.3470158014113305</v>
       </c>
+      <c r="G910">
+        <v>-0.3470158014113305</v>
+      </c>
     </row>
     <row r="911">
       <c r="A911">
@@ -15855,6 +18587,9 @@
       <c r="F911">
         <v>-0.269432871267816</v>
       </c>
+      <c r="G911">
+        <v>-0.269432871267816</v>
+      </c>
     </row>
     <row r="912">
       <c r="A912">
@@ -15872,6 +18607,9 @@
       <c r="F912">
         <v>-0.3926236998097539</v>
       </c>
+      <c r="G912">
+        <v>-0.3926236998097539</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913">
@@ -15889,6 +18627,9 @@
       <c r="F913">
         <v>-0.4076718719451798</v>
       </c>
+      <c r="G913">
+        <v>-0.4076718719451798</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914">
@@ -15906,6 +18647,9 @@
       <c r="F914">
         <v>0.2734404304299797</v>
       </c>
+      <c r="G914">
+        <v>0.2734404304299797</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915">
@@ -15923,6 +18667,9 @@
       <c r="F915">
         <v>1.188381792585155</v>
       </c>
+      <c r="G915">
+        <v>1.188381792585155</v>
+      </c>
     </row>
     <row r="916">
       <c r="A916">
@@ -15940,6 +18687,9 @@
       <c r="F916">
         <v>1.475099445904001</v>
       </c>
+      <c r="G916">
+        <v>1.475099445904001</v>
+      </c>
     </row>
     <row r="917">
       <c r="A917">
@@ -15957,6 +18707,9 @@
       <c r="F917">
         <v>1.689197450292846</v>
       </c>
+      <c r="G917">
+        <v>1.689197450292846</v>
+      </c>
     </row>
     <row r="918">
       <c r="A918">
@@ -15974,6 +18727,9 @@
       <c r="F918">
         <v>2.11398016951239</v>
       </c>
+      <c r="G918">
+        <v>2.11398016951239</v>
+      </c>
     </row>
     <row r="919">
       <c r="A919">
@@ -15991,6 +18747,9 @@
       <c r="F919">
         <v>0.216095836414689</v>
       </c>
+      <c r="G919">
+        <v>0.216095836414689</v>
+      </c>
     </row>
     <row r="920">
       <c r="A920">
@@ -16008,6 +18767,9 @@
       <c r="F920">
         <v>0.7920024470562903</v>
       </c>
+      <c r="G920">
+        <v>0.7920024470562903</v>
+      </c>
     </row>
     <row r="921">
       <c r="A921">
@@ -16025,6 +18787,9 @@
       <c r="F921">
         <v>0.8801831228136454</v>
       </c>
+      <c r="G921">
+        <v>0.8801831228136454</v>
+      </c>
     </row>
     <row r="922">
       <c r="A922">
@@ -16042,6 +18807,9 @@
       <c r="F922">
         <v>0.7991162114126716</v>
       </c>
+      <c r="G922">
+        <v>0.7991162114126716</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923">
@@ -16059,6 +18827,9 @@
       <c r="F923">
         <v>0.6977171214349542</v>
       </c>
+      <c r="G923">
+        <v>0.6977171214349542</v>
+      </c>
     </row>
     <row r="924">
       <c r="A924">
@@ -16076,6 +18847,9 @@
       <c r="F924">
         <v>0.1574681533778809</v>
       </c>
+      <c r="G924">
+        <v>0.1574681533778809</v>
+      </c>
     </row>
     <row r="925">
       <c r="A925">
@@ -16093,6 +18867,9 @@
       <c r="F925">
         <v>-0.6878407952789635</v>
       </c>
+      <c r="G925">
+        <v>-0.6878407952789635</v>
+      </c>
     </row>
     <row r="926">
       <c r="A926">
@@ -16110,6 +18887,9 @@
       <c r="F926">
         <v>-0.5582486533924211</v>
       </c>
+      <c r="G926">
+        <v>-0.5582486533924211</v>
+      </c>
     </row>
     <row r="927">
       <c r="A927">
@@ -16127,6 +18907,9 @@
       <c r="F927">
         <v>-0.6282919575482442</v>
       </c>
+      <c r="G927">
+        <v>-0.6282919575482442</v>
+      </c>
     </row>
     <row r="928">
       <c r="A928">
@@ -16144,6 +18927,9 @@
       <c r="F928">
         <v>-0.5683409690661548</v>
       </c>
+      <c r="G928">
+        <v>-0.5683409690661548</v>
+      </c>
     </row>
     <row r="929">
       <c r="A929">
@@ -16161,6 +18947,9 @@
       <c r="F929">
         <v>0.1505163249475846</v>
       </c>
+      <c r="G929">
+        <v>0.1505163249475846</v>
+      </c>
     </row>
     <row r="930">
       <c r="A930">
@@ -16178,6 +18967,9 @@
       <c r="F930">
         <v>0.1322067571207601</v>
       </c>
+      <c r="G930">
+        <v>0.1322067571207601</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931">
@@ -16195,6 +18987,9 @@
       <c r="F931">
         <v>0.1521648123649532</v>
       </c>
+      <c r="G931">
+        <v>0.1521648123649532</v>
+      </c>
     </row>
     <row r="932">
       <c r="A932">
@@ -16212,6 +19007,9 @@
       <c r="F932">
         <v>-0.01658537303926002</v>
       </c>
+      <c r="G932">
+        <v>-0.01658537303926002</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933">
@@ -16229,6 +19027,9 @@
       <c r="F933">
         <v>-0.120962990543711</v>
       </c>
+      <c r="G933">
+        <v>-0.120962990543711</v>
+      </c>
     </row>
     <row r="934">
       <c r="A934">
@@ -16246,6 +19047,9 @@
       <c r="F934">
         <v>-0.1046224488684628</v>
       </c>
+      <c r="G934">
+        <v>-0.1046224488684628</v>
+      </c>
     </row>
     <row r="935">
       <c r="A935">
@@ -16263,6 +19067,9 @@
       <c r="F935">
         <v>-0.7780561688852845</v>
       </c>
+      <c r="G935">
+        <v>-0.7780561688852845</v>
+      </c>
     </row>
     <row r="936">
       <c r="A936">
@@ -16280,6 +19087,9 @@
       <c r="F936">
         <v>-0.4451346065951152</v>
       </c>
+      <c r="G936">
+        <v>-0.4451346065951152</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937">
@@ -16297,6 +19107,9 @@
       <c r="F937">
         <v>-0.6581252609440557</v>
       </c>
+      <c r="G937">
+        <v>-0.6581252609440557</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938">
@@ -16314,6 +19127,9 @@
       <c r="F938">
         <v>-0.5162744750504067</v>
       </c>
+      <c r="G938">
+        <v>-0.5162744750504067</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939">
@@ -16331,6 +19147,9 @@
       <c r="F939">
         <v>0.2252763735233158</v>
       </c>
+      <c r="G939">
+        <v>0.2252763735233158</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940">
@@ -16348,6 +19167,9 @@
       <c r="F940">
         <v>0.4313880848123411</v>
       </c>
+      <c r="G940">
+        <v>0.4313880848123411</v>
+      </c>
     </row>
     <row r="941">
       <c r="A941">
@@ -16365,6 +19187,9 @@
       <c r="F941">
         <v>0.4436158976245727</v>
       </c>
+      <c r="G941">
+        <v>0.4436158976245727</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942">
@@ -16382,6 +19207,9 @@
       <c r="F942">
         <v>0.2812677991552214</v>
       </c>
+      <c r="G942">
+        <v>0.2812677991552214</v>
+      </c>
     </row>
     <row r="943">
       <c r="A943">
@@ -16399,6 +19227,9 @@
       <c r="F943">
         <v>0.1426669219608456</v>
       </c>
+      <c r="G943">
+        <v>0.1426669219608456</v>
+      </c>
     </row>
     <row r="944">
       <c r="A944">
@@ -16416,6 +19247,9 @@
       <c r="F944">
         <v>-0.2381649409941662</v>
       </c>
+      <c r="G944">
+        <v>-0.2381649409941662</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945">
@@ -16433,6 +19267,9 @@
       <c r="F945">
         <v>-1.142941760125374</v>
       </c>
+      <c r="G945">
+        <v>-1.142941760125374</v>
+      </c>
     </row>
     <row r="946">
       <c r="A946">
@@ -16450,6 +19287,9 @@
       <c r="F946">
         <v>-0.8631490235337225</v>
       </c>
+      <c r="G946">
+        <v>-0.8631490235337225</v>
+      </c>
     </row>
     <row r="947">
       <c r="A947">
@@ -16467,6 +19307,9 @@
       <c r="F947">
         <v>-0.8618571537411639</v>
       </c>
+      <c r="G947">
+        <v>-0.8618571537411639</v>
+      </c>
     </row>
     <row r="948">
       <c r="A948">
@@ -16484,6 +19327,9 @@
       <c r="F948">
         <v>-0.7048579263805596</v>
       </c>
+      <c r="G948">
+        <v>-0.7048579263805596</v>
+      </c>
     </row>
     <row r="949">
       <c r="A949">
@@ -16501,6 +19347,9 @@
       <c r="F949">
         <v>0.4490942245955881</v>
       </c>
+      <c r="G949">
+        <v>0.4490942245955881</v>
+      </c>
     </row>
     <row r="950">
       <c r="A950">
@@ -16518,6 +19367,9 @@
       <c r="F950">
         <v>-1.459033769599264</v>
       </c>
+      <c r="G950">
+        <v>-1.459033769599264</v>
+      </c>
     </row>
     <row r="951">
       <c r="A951">
@@ -16535,6 +19387,9 @@
       <c r="F951">
         <v>0.7078053535122502</v>
       </c>
+      <c r="G951">
+        <v>0.7078053535122502</v>
+      </c>
     </row>
     <row r="952">
       <c r="A952">
@@ -16552,6 +19407,9 @@
       <c r="F952">
         <v>-0.5530233540808819</v>
       </c>
+      <c r="G952">
+        <v>-0.5530233540808819</v>
+      </c>
     </row>
     <row r="953">
       <c r="A953">
@@ -16569,6 +19427,9 @@
       <c r="F953">
         <v>-0.02507934927909043</v>
       </c>
+      <c r="G953">
+        <v>-0.02507934927909043</v>
+      </c>
     </row>
     <row r="954">
       <c r="A954">
@@ -16586,6 +19447,9 @@
       <c r="F954">
         <v>0.1107918326419911</v>
       </c>
+      <c r="G954">
+        <v>0.1107918326419911</v>
+      </c>
     </row>
     <row r="955">
       <c r="A955">
@@ -16603,6 +19467,9 @@
       <c r="F955">
         <v>-0.04357935321413775</v>
       </c>
+      <c r="G955">
+        <v>-0.04357935321413775</v>
+      </c>
     </row>
     <row r="956">
       <c r="A956">
@@ -16620,6 +19487,9 @@
       <c r="F956">
         <v>0.004305960239060702</v>
       </c>
+      <c r="G956">
+        <v>0.004305960239060702</v>
+      </c>
     </row>
     <row r="957">
       <c r="A957">
@@ -16637,6 +19507,9 @@
       <c r="F957">
         <v>-0.1516518604912567</v>
       </c>
+      <c r="G957">
+        <v>-0.1516518604912567</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958">
@@ -16654,6 +19527,9 @@
       <c r="F958">
         <v>-0.2283491531811017</v>
       </c>
+      <c r="G958">
+        <v>-0.2283491531811017</v>
+      </c>
     </row>
     <row r="959">
       <c r="A959">
@@ -16671,6 +19547,9 @@
       <c r="F959">
         <v>-0.1918446625217221</v>
       </c>
+      <c r="G959">
+        <v>-0.1918446625217221</v>
+      </c>
     </row>
     <row r="960">
       <c r="A960">
@@ -16688,6 +19567,9 @@
       <c r="F960">
         <v>-1.382410041200445</v>
       </c>
+      <c r="G960">
+        <v>-1.382410041200445</v>
+      </c>
     </row>
     <row r="961">
       <c r="A961">
@@ -16705,6 +19587,9 @@
       <c r="F961">
         <v>-1.047807882091885</v>
       </c>
+      <c r="G961">
+        <v>-1.047807882091885</v>
+      </c>
     </row>
     <row r="962">
       <c r="A962">
@@ -16722,6 +19607,9 @@
       <c r="F962">
         <v>-0.9739432070379805</v>
       </c>
+      <c r="G962">
+        <v>-0.9739432070379805</v>
+      </c>
     </row>
     <row r="963">
       <c r="A963">
@@ -16737,6 +19625,9 @@
         <v>0.09368412090893186</v>
       </c>
       <c r="F963">
+        <v>-0.7770282430106312</v>
+      </c>
+      <c r="G963">
         <v>-0.7770282430106312</v>
       </c>
     </row>
